--- a/output/Data and Chart Outputs/nz_gas.xlsx
+++ b/output/Data and Chart Outputs/nz_gas.xlsx
@@ -10,7 +10,9 @@
     <sheet name="Units" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Chart" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Chart - Storage" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Monthly" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Chart - Demand" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Monthly" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Quarterly consumption" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -451,6 +453,337 @@
 </chartSpace>
 </file>
 
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>New Zealand gas consumption by sector (MBIE, quarterly) (to Jun/26)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="0"/>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="stacked"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Chart - Demand'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="2A78D6"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Chart - Demand'!$A$2:$A$23</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Chart - Demand'!$B$2:$B$23</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Chart - Demand'!C1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="EB6834"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Chart - Demand'!$A$2:$A$23</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Chart - Demand'!$C$2:$C$23</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Chart - Demand'!D1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="1BAF7A"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Chart - Demand'!$A$2:$A$23</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Chart - Demand'!$D$2:$D$23</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Chart - Demand'!E1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="EDA100"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Chart - Demand'!$A$2:$A$23</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Chart - Demand'!$E$2:$E$23</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="4"/>
+          <order val="4"/>
+          <tx>
+            <strRef>
+              <f>'Chart - Demand'!F1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="E87BA4"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Chart - Demand'!$A$2:$A$23</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Chart - Demand'!$F$2:$F$23</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="5"/>
+          <order val="5"/>
+          <tx>
+            <strRef>
+              <f>'Chart - Demand'!G1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="008300"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Chart - Demand'!$A$2:$A$23</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Chart - Demand'!$G$2:$G$23</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="6"/>
+          <order val="6"/>
+          <tx>
+            <strRef>
+              <f>'Chart - Demand'!H1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="4A3AA7"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Chart - Demand'!$A$2:$A$23</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Chart - Demand'!$H$2:$H$23</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="7"/>
+          <order val="7"/>
+          <tx>
+            <strRef>
+              <f>'Chart - Demand'!I1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="E34948"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Chart - Demand'!$A$2:$A$23</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Chart - Demand'!$I$2:$I$23</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="30"/>
+        <overlap val="100"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="b"/>
+        <numFmt formatCode="mmm/yy" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr/>
+          </a:p>
+        </txPr>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+        <tickLblSkip val="1"/>
+        <tickMarkSkip val="1"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>PJ per quarter</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+          <overlay val="0"/>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+      <spPr>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <overlay val="0"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+  <spPr>
+    <a:ln>
+      <a:noFill/>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
+</chartSpace>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -483,6 +816,33 @@
   <oneCellAnchor>
     <from>
       <col>3</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="10080000" cy="4680000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -2214,6 +2574,709 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Gross Production</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Gas Reinjected</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>LPG extracted</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Gas Flared</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Net Production</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Manufactured Production</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Stock Change</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Electricity Generation</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="n">
+        <v>44286</v>
+      </c>
+      <c r="B2" t="n">
+        <v>40.8657</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.614</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.2896</v>
+      </c>
+      <c r="F2" t="n">
+        <v>38.9621</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.1016</v>
+      </c>
+      <c r="I2" t="n">
+        <v>6.7683</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n">
+        <v>44377</v>
+      </c>
+      <c r="B3" t="n">
+        <v>40.699</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.6376</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.2616</v>
+      </c>
+      <c r="F3" t="n">
+        <v>38.7998</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-0.07539999999999999</v>
+      </c>
+      <c r="I3" t="n">
+        <v>9.3604</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="B4" t="n">
+        <v>41.0685</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.6871</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.2473</v>
+      </c>
+      <c r="F4" t="n">
+        <v>39.1341</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.264</v>
+      </c>
+      <c r="I4" t="n">
+        <v>9.617900000000001</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>44561</v>
+      </c>
+      <c r="B5" t="n">
+        <v>43.0301</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.2333</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.9104</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.2573</v>
+      </c>
+      <c r="F5" t="n">
+        <v>40.6292</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.799</v>
+      </c>
+      <c r="I5" t="n">
+        <v>4.7461</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="B6" t="n">
+        <v>41.5058</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.9425</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.2421</v>
+      </c>
+      <c r="F6" t="n">
+        <v>39.3193</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-0.3783</v>
+      </c>
+      <c r="I6" t="n">
+        <v>8.939</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="B7" t="n">
+        <v>36.9326</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.833</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.2229</v>
+      </c>
+      <c r="F7" t="n">
+        <v>34.8767</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-2.422</v>
+      </c>
+      <c r="I7" t="n">
+        <v>11.0062</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
+        <v>44834</v>
+      </c>
+      <c r="B8" t="n">
+        <v>37.1878</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.0051</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.8316</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.1982</v>
+      </c>
+      <c r="F8" t="n">
+        <v>35.1529</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="I8" t="n">
+        <v>7.5827</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>44926</v>
+      </c>
+      <c r="B9" t="n">
+        <v>35.5811</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.4739</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.2353</v>
+      </c>
+      <c r="F9" t="n">
+        <v>33.8719</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-3.9054</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.0918</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>45016</v>
+      </c>
+      <c r="B10" t="n">
+        <v>39.8363</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.6963</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.2826</v>
+      </c>
+      <c r="F10" t="n">
+        <v>37.8433</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0.0825</v>
+      </c>
+      <c r="I10" t="n">
+        <v>7.6181</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>45107</v>
+      </c>
+      <c r="B11" t="n">
+        <v>40.132</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.0432</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.7461</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.2006</v>
+      </c>
+      <c r="F11" t="n">
+        <v>38.1422</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.1932</v>
+      </c>
+      <c r="I11" t="n">
+        <v>6.3837</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>45199</v>
+      </c>
+      <c r="B12" t="n">
+        <v>40.3103</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.7766</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.2361</v>
+      </c>
+      <c r="F12" t="n">
+        <v>38.2976</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-1.0439</v>
+      </c>
+      <c r="I12" t="n">
+        <v>13.4095</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>45291</v>
+      </c>
+      <c r="B13" t="n">
+        <v>35.2398</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.2354</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.1897</v>
+      </c>
+      <c r="F13" t="n">
+        <v>33.8146</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-0.9633</v>
+      </c>
+      <c r="I13" t="n">
+        <v>5.2609</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>45382</v>
+      </c>
+      <c r="B14" t="n">
+        <v>33.9086</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.6695</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.1711</v>
+      </c>
+      <c r="F14" t="n">
+        <v>32.068</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-0.7711</v>
+      </c>
+      <c r="I14" t="n">
+        <v>8.6853</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>45473</v>
+      </c>
+      <c r="B15" t="n">
+        <v>32.9149</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.5958</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.2752</v>
+      </c>
+      <c r="F15" t="n">
+        <v>31.044</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-0.6158</v>
+      </c>
+      <c r="I15" t="n">
+        <v>8.7836</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
+        <v>45565</v>
+      </c>
+      <c r="B16" t="n">
+        <v>32.1622</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.5412</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.3959</v>
+      </c>
+      <c r="F16" t="n">
+        <v>30.2251</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.7935</v>
+      </c>
+      <c r="I16" t="n">
+        <v>9.1503</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>45657</v>
+      </c>
+      <c r="B17" t="n">
+        <v>27.9034</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.3096</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.2953</v>
+      </c>
+      <c r="F17" t="n">
+        <v>26.2984</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.3368</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3.0137</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="n">
+        <v>45747</v>
+      </c>
+      <c r="B18" t="n">
+        <v>27.6733</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.3674</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.3769</v>
+      </c>
+      <c r="F18" t="n">
+        <v>25.929</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-2.4564</v>
+      </c>
+      <c r="I18" t="n">
+        <v>8.8843</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>45838</v>
+      </c>
+      <c r="B19" t="n">
+        <v>27.3417</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.0448</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.3006</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.2677</v>
+      </c>
+      <c r="F19" t="n">
+        <v>25.7286</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.9331</v>
+      </c>
+      <c r="I19" t="n">
+        <v>8.7065</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="B20" t="n">
+        <v>27.0764</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.0439</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.2304</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.3041</v>
+      </c>
+      <c r="F20" t="n">
+        <v>25.498</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-2.3557</v>
+      </c>
+      <c r="I20" t="n">
+        <v>6.9756</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B21" t="n">
+        <v>26.7693</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.0098</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.1788</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.2956</v>
+      </c>
+      <c r="F21" t="n">
+        <v>25.2851</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>3.2977</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.2597</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B22" t="n">
+        <v>22.9596</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.0529</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.842</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.2439</v>
+      </c>
+      <c r="F22" t="n">
+        <v>21.8207</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.5709</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.875</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B23" t="n">
+        <v>21.8081</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.0575</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.915</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.1294</v>
+      </c>
+      <c r="F23" t="n">
+        <v>20.7063</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.2786</v>
+      </c>
+      <c r="I23" t="n">
+        <v>5.3746</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:J200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -8640,4 +9703,4821 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:W67"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Gross Production</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Gas Reinjected</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>LPG extracted</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Gas Flared</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Net Production</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Manufactured Production</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Stock Change</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Electricity Generation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Cogeneration</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Other Transformation</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Production losses and own use</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Transmission and distribution losses</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Non-Energy Use</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Agriculture/ Forestry/ Fishing</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Food Processing</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Wood, Pulp, Paper, and Printing</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Chemicals</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Basic Metals</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Residential</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Transport</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n">
+        <v>40268</v>
+      </c>
+      <c r="B2" t="n">
+        <v>45.8497</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1.2278</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.744</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1.8005</v>
+      </c>
+      <c r="F2" t="n">
+        <v>42.0774</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.4491</v>
+      </c>
+      <c r="I2" t="n">
+        <v>13.0898</v>
+      </c>
+      <c r="J2" t="n">
+        <v>5.2061</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.7378</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.1146</v>
+      </c>
+      <c r="N2" t="n">
+        <v>6.4037</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.2661</v>
+      </c>
+      <c r="P2" t="n">
+        <v>3.9674</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.0262</v>
+      </c>
+      <c r="R2" t="n">
+        <v>4.4699</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.7028</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.6528</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.3965</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.8814</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.0106</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="n">
+        <v>40359</v>
+      </c>
+      <c r="B3" t="n">
+        <v>48.8887</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.9951</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1.4998</v>
+      </c>
+      <c r="F3" t="n">
+        <v>45.2638</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.2784</v>
+      </c>
+      <c r="I3" t="n">
+        <v>17.548</v>
+      </c>
+      <c r="J3" t="n">
+        <v>4.4002</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2.0228</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.1895</v>
+      </c>
+      <c r="N3" t="n">
+        <v>6.5541</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.4408</v>
+      </c>
+      <c r="P3" t="n">
+        <v>3.3491</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.3282</v>
+      </c>
+      <c r="R3" t="n">
+        <v>4.7023</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.7826</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.7013</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.866</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.5376</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.008399999999999999</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="n">
+        <v>40451</v>
+      </c>
+      <c r="B4" t="n">
+        <v>52.5553</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.8971</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.1258</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1.9675</v>
+      </c>
+      <c r="F4" t="n">
+        <v>48.5649</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.0164</v>
+      </c>
+      <c r="I4" t="n">
+        <v>18.495</v>
+      </c>
+      <c r="J4" t="n">
+        <v>4.9262</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>2.085</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.2319</v>
+      </c>
+      <c r="N4" t="n">
+        <v>6.0404</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.4367</v>
+      </c>
+      <c r="P4" t="n">
+        <v>3.1477</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.4406</v>
+      </c>
+      <c r="R4" t="n">
+        <v>4.7263</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.7877999999999999</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.7225</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2.1047</v>
+      </c>
+      <c r="V4" t="n">
+        <v>2.416</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.0105</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n">
+        <v>40543</v>
+      </c>
+      <c r="B5" t="n">
+        <v>47.3866</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.7563</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.9921</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2.2019</v>
+      </c>
+      <c r="F5" t="n">
+        <v>43.4363</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.1409</v>
+      </c>
+      <c r="I5" t="n">
+        <v>13.4613</v>
+      </c>
+      <c r="J5" t="n">
+        <v>4.8692</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2.0153</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.1459</v>
+      </c>
+      <c r="N5" t="n">
+        <v>6.4451</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.3272</v>
+      </c>
+      <c r="P5" t="n">
+        <v>4.6955</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.0498</v>
+      </c>
+      <c r="R5" t="n">
+        <v>4.9671</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.7314000000000001</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.7634</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.4787</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.1572</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.0048</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n">
+        <v>40633</v>
+      </c>
+      <c r="B6" t="n">
+        <v>38.6109</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.854</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.5268</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2.0159</v>
+      </c>
+      <c r="F6" t="n">
+        <v>35.2142</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.3627</v>
+      </c>
+      <c r="I6" t="n">
+        <v>11.6842</v>
+      </c>
+      <c r="J6" t="n">
+        <v>4.269</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.8075</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.1504</v>
+      </c>
+      <c r="N6" t="n">
+        <v>6.1155</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.2665</v>
+      </c>
+      <c r="P6" t="n">
+        <v>3.5479</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.0239</v>
+      </c>
+      <c r="R6" t="n">
+        <v>4.7601</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.6969</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.7008</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.9648</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.7371</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.0052</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>40724</v>
+      </c>
+      <c r="B7" t="n">
+        <v>43.6201</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1.1188</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.8108</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1.529</v>
+      </c>
+      <c r="F7" t="n">
+        <v>40.1615</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.8251</v>
+      </c>
+      <c r="I7" t="n">
+        <v>12.3604</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.2976</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2.0949</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.2144</v>
+      </c>
+      <c r="N7" t="n">
+        <v>6.3715</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.5168</v>
+      </c>
+      <c r="P7" t="n">
+        <v>3.1903</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.4316</v>
+      </c>
+      <c r="R7" t="n">
+        <v>5.0242</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.7602</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.7406</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.5777</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.4284</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.0077</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>40816</v>
+      </c>
+      <c r="B8" t="n">
+        <v>51.3859</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1.4082</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.4126</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1.6965</v>
+      </c>
+      <c r="F8" t="n">
+        <v>46.8686</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.4214</v>
+      </c>
+      <c r="I8" t="n">
+        <v>16.1244</v>
+      </c>
+      <c r="J8" t="n">
+        <v>5.5517</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2.6768</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.2951</v>
+      </c>
+      <c r="N8" t="n">
+        <v>5.9985</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.5716</v>
+      </c>
+      <c r="P8" t="n">
+        <v>3.8058</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.4006</v>
+      </c>
+      <c r="R8" t="n">
+        <v>4.8095</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.7828000000000001</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.8051</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.7332</v>
+      </c>
+      <c r="V8" t="n">
+        <v>2.2695</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>40908</v>
+      </c>
+      <c r="B9" t="n">
+        <v>42.5431</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1.183</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.9017</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.2464</v>
+      </c>
+      <c r="F9" t="n">
+        <v>38.2121</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.6846</v>
+      </c>
+      <c r="I9" t="n">
+        <v>11.128</v>
+      </c>
+      <c r="J9" t="n">
+        <v>4.6359</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2.0627</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.2004</v>
+      </c>
+      <c r="N9" t="n">
+        <v>5.8647</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.3179</v>
+      </c>
+      <c r="P9" t="n">
+        <v>4.6379</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.1697</v>
+      </c>
+      <c r="R9" t="n">
+        <v>4.3261</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.7068</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.6453</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.3743</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.1825</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.039</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>40999</v>
+      </c>
+      <c r="B10" t="n">
+        <v>42.3317</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.3878</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.8743</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.4229</v>
+      </c>
+      <c r="F10" t="n">
+        <v>37.6467</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0.1333</v>
+      </c>
+      <c r="I10" t="n">
+        <v>13.6476</v>
+      </c>
+      <c r="J10" t="n">
+        <v>4.6769</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.8644</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.1889</v>
+      </c>
+      <c r="N10" t="n">
+        <v>4.9344</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.287</v>
+      </c>
+      <c r="P10" t="n">
+        <v>4.4143</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.1458</v>
+      </c>
+      <c r="R10" t="n">
+        <v>3.8173</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.6631</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.3814</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.8318</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>41090</v>
+      </c>
+      <c r="B11" t="n">
+        <v>49.7578</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1.4514</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.9067</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.477</v>
+      </c>
+      <c r="F11" t="n">
+        <v>44.9227</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0.1555</v>
+      </c>
+      <c r="I11" t="n">
+        <v>16.5657</v>
+      </c>
+      <c r="J11" t="n">
+        <v>4.7457</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.1456</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.2668</v>
+      </c>
+      <c r="N11" t="n">
+        <v>6.3308</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.4328</v>
+      </c>
+      <c r="P11" t="n">
+        <v>3.7738</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.5505</v>
+      </c>
+      <c r="R11" t="n">
+        <v>4.8653</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.765</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.7518</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.1235</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.673</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.0179</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>41182</v>
+      </c>
+      <c r="B12" t="n">
+        <v>52.5468</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.4291</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2.2594</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.1251</v>
+      </c>
+      <c r="F12" t="n">
+        <v>48.7331</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-0.2563</v>
+      </c>
+      <c r="I12" t="n">
+        <v>14.0412</v>
+      </c>
+      <c r="J12" t="n">
+        <v>4.934</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2.0148</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.2505</v>
+      </c>
+      <c r="N12" t="n">
+        <v>9.894399999999999</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.503</v>
+      </c>
+      <c r="P12" t="n">
+        <v>3.9321</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.6623</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6.8748</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.8341</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.7801</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.5686</v>
+      </c>
+      <c r="V12" t="n">
+        <v>2.4171</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.0094</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>41274</v>
+      </c>
+      <c r="B13" t="n">
+        <v>43.763</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.4505</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.8429</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.7354000000000001</v>
+      </c>
+      <c r="F13" t="n">
+        <v>40.7342</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-1.4003</v>
+      </c>
+      <c r="I13" t="n">
+        <v>8.7105</v>
+      </c>
+      <c r="J13" t="n">
+        <v>4.4947</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.7311</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.171</v>
+      </c>
+      <c r="N13" t="n">
+        <v>10.5033</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.3397</v>
+      </c>
+      <c r="P13" t="n">
+        <v>4.5178</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.094</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7.1322</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.7651</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.6741</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.7947</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.3544</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.0077</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>41364</v>
+      </c>
+      <c r="B14" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1.5476</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.7539</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.7157</v>
+      </c>
+      <c r="F14" t="n">
+        <v>42.8827</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-0.1546</v>
+      </c>
+      <c r="I14" t="n">
+        <v>14.0195</v>
+      </c>
+      <c r="J14" t="n">
+        <v>4.9645</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.7011</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.1983</v>
+      </c>
+      <c r="N14" t="n">
+        <v>8.8019</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.2325</v>
+      </c>
+      <c r="P14" t="n">
+        <v>3.795</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.9699</v>
+      </c>
+      <c r="R14" t="n">
+        <v>5.8552</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.7066</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.6463</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.3701</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.734</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.0074</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>41455</v>
+      </c>
+      <c r="B15" t="n">
+        <v>55.2002</v>
+      </c>
+      <c r="C15" t="n">
+        <v>3.8389</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.0297</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.9019</v>
+      </c>
+      <c r="F15" t="n">
+        <v>48.4297</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-0.2229</v>
+      </c>
+      <c r="I15" t="n">
+        <v>16.3365</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.896</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.7934</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.245</v>
+      </c>
+      <c r="N15" t="n">
+        <v>10.0578</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.4492</v>
+      </c>
+      <c r="P15" t="n">
+        <v>3.1384</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.9856</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7.5774</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.989</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.8112</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.0977</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.6996</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0.0053</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>41547</v>
+      </c>
+      <c r="B16" t="n">
+        <v>54.3692</v>
+      </c>
+      <c r="C16" t="n">
+        <v>2.9721</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.2003</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.5572</v>
+      </c>
+      <c r="F16" t="n">
+        <v>48.6396</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.7188</v>
+      </c>
+      <c r="I16" t="n">
+        <v>14.6054</v>
+      </c>
+      <c r="J16" t="n">
+        <v>4.0342</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.4073</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.2679</v>
+      </c>
+      <c r="N16" t="n">
+        <v>9.823499999999999</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.5052</v>
+      </c>
+      <c r="P16" t="n">
+        <v>3.7146</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.1239</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7.1856</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.2329</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.8454</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.5587</v>
+      </c>
+      <c r="V16" t="n">
+        <v>2.4305</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.008399999999999999</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>41639</v>
+      </c>
+      <c r="B17" t="n">
+        <v>48.0742</v>
+      </c>
+      <c r="C17" t="n">
+        <v>2.4451</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.9075</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.5197000000000001</v>
+      </c>
+      <c r="F17" t="n">
+        <v>43.2019</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.6969</v>
+      </c>
+      <c r="I17" t="n">
+        <v>9.0886</v>
+      </c>
+      <c r="J17" t="n">
+        <v>4.2094</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.2476</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.1892</v>
+      </c>
+      <c r="N17" t="n">
+        <v>10.8918</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="P17" t="n">
+        <v>4.5339</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.8623</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7.5705</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.5626</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.8557</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.7385</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.3137</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0.0072</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>41729</v>
+      </c>
+      <c r="B18" t="n">
+        <v>53.6147</v>
+      </c>
+      <c r="C18" t="n">
+        <v>4.4604</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.8382</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.9274</v>
+      </c>
+      <c r="F18" t="n">
+        <v>46.3888</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-0.8499</v>
+      </c>
+      <c r="I18" t="n">
+        <v>11.4824</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.9247</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.5223</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.1806</v>
+      </c>
+      <c r="N18" t="n">
+        <v>13.6021</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.2996</v>
+      </c>
+      <c r="P18" t="n">
+        <v>3.8973</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.7306</v>
+      </c>
+      <c r="R18" t="n">
+        <v>8.7173</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.1404</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0.7103</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.6216</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0.9108000000000001</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0.0056</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>41820</v>
+      </c>
+      <c r="B19" t="n">
+        <v>59.8697</v>
+      </c>
+      <c r="C19" t="n">
+        <v>5.0092</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.3957</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.6707</v>
+      </c>
+      <c r="F19" t="n">
+        <v>51.7942</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.576</v>
+      </c>
+      <c r="I19" t="n">
+        <v>11.631</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.169</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.4867</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.2051</v>
+      </c>
+      <c r="N19" t="n">
+        <v>14.9545</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.4176</v>
+      </c>
+      <c r="P19" t="n">
+        <v>3.0094</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.0081</v>
+      </c>
+      <c r="R19" t="n">
+        <v>10.2886</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.8771</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.0308</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2.1991</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.5712</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>41912</v>
+      </c>
+      <c r="B20" t="n">
+        <v>64.3142</v>
+      </c>
+      <c r="C20" t="n">
+        <v>5.3295</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2.5879</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.6516</v>
+      </c>
+      <c r="F20" t="n">
+        <v>55.7451</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.8113</v>
+      </c>
+      <c r="I20" t="n">
+        <v>9.6686</v>
+      </c>
+      <c r="J20" t="n">
+        <v>4.7594</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.6292</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.2413</v>
+      </c>
+      <c r="N20" t="n">
+        <v>15.8544</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.5374</v>
+      </c>
+      <c r="P20" t="n">
+        <v>3.9503</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.257</v>
+      </c>
+      <c r="R20" t="n">
+        <v>10.9441</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.8882</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.1307</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2.8651</v>
+      </c>
+      <c r="V20" t="n">
+        <v>2.5762</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0.0054</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>42004</v>
+      </c>
+      <c r="B21" t="n">
+        <v>55.7289</v>
+      </c>
+      <c r="C21" t="n">
+        <v>3.0021</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2.0648</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="F21" t="n">
+        <v>50.0791</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-0.9046999999999999</v>
+      </c>
+      <c r="I21" t="n">
+        <v>9.214</v>
+      </c>
+      <c r="J21" t="n">
+        <v>4.6908</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.8074</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.1927</v>
+      </c>
+      <c r="N21" t="n">
+        <v>14.7668</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.3772</v>
+      </c>
+      <c r="P21" t="n">
+        <v>4.969</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.9746</v>
+      </c>
+      <c r="R21" t="n">
+        <v>10.0025</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.6183</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0.7519</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2.1957</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.5438</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0.0056</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>42094</v>
+      </c>
+      <c r="B22" t="n">
+        <v>52.0399</v>
+      </c>
+      <c r="C22" t="n">
+        <v>2.5726</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.0335</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.8263</v>
+      </c>
+      <c r="F22" t="n">
+        <v>46.6074</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-0.366</v>
+      </c>
+      <c r="I22" t="n">
+        <v>11.0156</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3.9155</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.4689</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.1614</v>
+      </c>
+      <c r="N22" t="n">
+        <v>13.0231</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.266</v>
+      </c>
+      <c r="P22" t="n">
+        <v>4.4343</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.7655</v>
+      </c>
+      <c r="R22" t="n">
+        <v>8.3886</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.5617</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0.6563</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.6126</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0.862</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0.0023</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>42185</v>
+      </c>
+      <c r="B23" t="n">
+        <v>56.4589</v>
+      </c>
+      <c r="C23" t="n">
+        <v>3.7414</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2.141</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1.7657</v>
+      </c>
+      <c r="F23" t="n">
+        <v>48.8108</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.2866</v>
+      </c>
+      <c r="I23" t="n">
+        <v>10.7194</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3.265</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.5412</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.2336</v>
+      </c>
+      <c r="N23" t="n">
+        <v>13.0854</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.4662</v>
+      </c>
+      <c r="P23" t="n">
+        <v>3.2245</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.947</v>
+      </c>
+      <c r="R23" t="n">
+        <v>9.1617</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.6153999999999999</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0.8326</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2.3443</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.6204</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0.0063</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>42277</v>
+      </c>
+      <c r="B24" t="n">
+        <v>58.6555</v>
+      </c>
+      <c r="C24" t="n">
+        <v>3.655</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2.2602</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2.3327</v>
+      </c>
+      <c r="F24" t="n">
+        <v>50.4076</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-1.2256</v>
+      </c>
+      <c r="I24" t="n">
+        <v>11.0218</v>
+      </c>
+      <c r="J24" t="n">
+        <v>4.4351</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.6251</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.2608</v>
+      </c>
+      <c r="N24" t="n">
+        <v>12.8465</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.5566</v>
+      </c>
+      <c r="P24" t="n">
+        <v>4.0891</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.0863</v>
+      </c>
+      <c r="R24" t="n">
+        <v>9.0932</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.6274999999999999</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0.8476</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2.9537</v>
+      </c>
+      <c r="V24" t="n">
+        <v>2.8424</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0.0065</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>42369</v>
+      </c>
+      <c r="B25" t="n">
+        <v>49.7091</v>
+      </c>
+      <c r="C25" t="n">
+        <v>3.1038</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1.6914</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2.1299</v>
+      </c>
+      <c r="F25" t="n">
+        <v>42.784</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-0.8117</v>
+      </c>
+      <c r="I25" t="n">
+        <v>8.2879</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3.8162</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.4226</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.1475</v>
+      </c>
+      <c r="N25" t="n">
+        <v>11.2271</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.3594</v>
+      </c>
+      <c r="P25" t="n">
+        <v>5.2886</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.0478</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7.9095</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.6442</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.774</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2.1022</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.5513</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0.0057</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n">
+        <v>42460</v>
+      </c>
+      <c r="B26" t="n">
+        <v>51.7583</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1.7669</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2.0527</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1.832</v>
+      </c>
+      <c r="F26" t="n">
+        <v>46.1067</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.3828</v>
+      </c>
+      <c r="I26" t="n">
+        <v>10.4179</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.4464</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.4318</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.1226</v>
+      </c>
+      <c r="N26" t="n">
+        <v>13.0178</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.2376</v>
+      </c>
+      <c r="P26" t="n">
+        <v>4.2857</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.9544</v>
+      </c>
+      <c r="R26" t="n">
+        <v>9.0023</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.6196</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0.7143</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.4754</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0.8318</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0.004</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>42551</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57.5845</v>
+      </c>
+      <c r="C27" t="n">
+        <v>3.5865</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1.611</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1.1799</v>
+      </c>
+      <c r="F27" t="n">
+        <v>51.2071</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1.3234</v>
+      </c>
+      <c r="I27" t="n">
+        <v>9.992699999999999</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2.7019</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.2662</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.1572</v>
+      </c>
+      <c r="N27" t="n">
+        <v>15.3219</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.4164</v>
+      </c>
+      <c r="P27" t="n">
+        <v>3.3241</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.1594</v>
+      </c>
+      <c r="R27" t="n">
+        <v>10.6046</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0.6455</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0.8239</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2.1162</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.4812</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0.0013</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n">
+        <v>42643</v>
+      </c>
+      <c r="B28" t="n">
+        <v>58.7089</v>
+      </c>
+      <c r="C28" t="n">
+        <v>2.8785</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1.6979</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1.6337</v>
+      </c>
+      <c r="F28" t="n">
+        <v>52.4989</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-1.1968</v>
+      </c>
+      <c r="I28" t="n">
+        <v>9.599</v>
+      </c>
+      <c r="J28" t="n">
+        <v>3.064</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.4485</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.1868</v>
+      </c>
+      <c r="N28" t="n">
+        <v>15.1606</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.5523</v>
+      </c>
+      <c r="P28" t="n">
+        <v>4.0019</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.3531</v>
+      </c>
+      <c r="R28" t="n">
+        <v>10.4673</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0.6358</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0.7986</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2.7902</v>
+      </c>
+      <c r="V28" t="n">
+        <v>2.5608</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0.0041</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>42735</v>
+      </c>
+      <c r="B29" t="n">
+        <v>52.6453</v>
+      </c>
+      <c r="C29" t="n">
+        <v>3.9314</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1.6455</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1.0326</v>
+      </c>
+      <c r="F29" t="n">
+        <v>46.0359</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.4569</v>
+      </c>
+      <c r="I29" t="n">
+        <v>6.5425</v>
+      </c>
+      <c r="J29" t="n">
+        <v>3.3725</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.2242</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.162</v>
+      </c>
+      <c r="N29" t="n">
+        <v>14.6509</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0.0785</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.5082</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.047</v>
+      </c>
+      <c r="R29" t="n">
+        <v>9.638299999999999</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0.5427</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0.6741</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.7047</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.5435</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0.004</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
+        <v>42825</v>
+      </c>
+      <c r="B30" t="n">
+        <v>51.4815</v>
+      </c>
+      <c r="C30" t="n">
+        <v>4.0306</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1.6542</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1.2137</v>
+      </c>
+      <c r="F30" t="n">
+        <v>44.5831</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>-0.4318</v>
+      </c>
+      <c r="I30" t="n">
+        <v>7.7581</v>
+      </c>
+      <c r="J30" t="n">
+        <v>3.3126</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1.376</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="N30" t="n">
+        <v>14.5859</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0.2631</v>
+      </c>
+      <c r="P30" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0.951</v>
+      </c>
+      <c r="R30" t="n">
+        <v>9.104900000000001</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0.5568</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0.8245</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.4438</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0.9809</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0.004</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>42916</v>
+      </c>
+      <c r="B31" t="n">
+        <v>51.4874</v>
+      </c>
+      <c r="C31" t="n">
+        <v>3.642</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1.9203</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1.4192</v>
+      </c>
+      <c r="F31" t="n">
+        <v>44.5059</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>-1.857</v>
+      </c>
+      <c r="I31" t="n">
+        <v>13.8957</v>
+      </c>
+      <c r="J31" t="n">
+        <v>3.0852</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1.4515</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.1663</v>
+      </c>
+      <c r="N31" t="n">
+        <v>10.0544</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0.4206</v>
+      </c>
+      <c r="P31" t="n">
+        <v>3.4087</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1.1856</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7.1444</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0.6419</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0.952</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2.0927</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.7559</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0.0038</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="n">
+        <v>43008</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57.646</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.3208</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2.0242</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1.3924</v>
+      </c>
+      <c r="F32" t="n">
+        <v>53.9088</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>-0.7159</v>
+      </c>
+      <c r="I32" t="n">
+        <v>13.2307</v>
+      </c>
+      <c r="J32" t="n">
+        <v>3.7921</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1.524</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.2014</v>
+      </c>
+      <c r="N32" t="n">
+        <v>13.6492</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0.4583</v>
+      </c>
+      <c r="P32" t="n">
+        <v>4.4013</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1.286</v>
+      </c>
+      <c r="R32" t="n">
+        <v>9.5717</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0.7037</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0.9921</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2.6518</v>
+      </c>
+      <c r="V32" t="n">
+        <v>2.6605</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0.0011</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="n">
+        <v>43100</v>
+      </c>
+      <c r="B33" t="n">
+        <v>55.2508</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1.9537</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1.5052</v>
+      </c>
+      <c r="F33" t="n">
+        <v>51.3687</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>-0.1169</v>
+      </c>
+      <c r="I33" t="n">
+        <v>10.8293</v>
+      </c>
+      <c r="J33" t="n">
+        <v>3.6919</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1.5322</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.1752</v>
+      </c>
+      <c r="N33" t="n">
+        <v>15.0261</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0.3078</v>
+      </c>
+      <c r="P33" t="n">
+        <v>5.1155</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1.309</v>
+      </c>
+      <c r="R33" t="n">
+        <v>9.7247</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0.6641</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0.9106</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.8727</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.425</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="n">
+        <v>43190</v>
+      </c>
+      <c r="B34" t="n">
+        <v>49.8006</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.2951</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1.8277</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1.3378</v>
+      </c>
+      <c r="F34" t="n">
+        <v>46.3401</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.1157</v>
+      </c>
+      <c r="I34" t="n">
+        <v>11.0349</v>
+      </c>
+      <c r="J34" t="n">
+        <v>3.4359</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>2.3766</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.1454</v>
+      </c>
+      <c r="N34" t="n">
+        <v>13.2713</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0.2021</v>
+      </c>
+      <c r="P34" t="n">
+        <v>3.814</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>1.0742</v>
+      </c>
+      <c r="R34" t="n">
+        <v>8.875400000000001</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0.6337</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0.8018</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.4464</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0.828</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="n">
+        <v>43281</v>
+      </c>
+      <c r="B35" t="n">
+        <v>40.5723</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.1144</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1.9373</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1.0974</v>
+      </c>
+      <c r="F35" t="n">
+        <v>37.4231</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.4312</v>
+      </c>
+      <c r="I35" t="n">
+        <v>9.110900000000001</v>
+      </c>
+      <c r="J35" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>1.4982</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.1622</v>
+      </c>
+      <c r="N35" t="n">
+        <v>7.4531</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0.3756</v>
+      </c>
+      <c r="P35" t="n">
+        <v>3.6852</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>1.2807</v>
+      </c>
+      <c r="R35" t="n">
+        <v>5.7516</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0.6708</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0.977</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2.2585</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.7572</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="n">
+        <v>43373</v>
+      </c>
+      <c r="B36" t="n">
+        <v>50.6799</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.0218</v>
+      </c>
+      <c r="D36" t="n">
+        <v>2.2876</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.7022</v>
+      </c>
+      <c r="F36" t="n">
+        <v>47.6683</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>-2.1069</v>
+      </c>
+      <c r="I36" t="n">
+        <v>10.082</v>
+      </c>
+      <c r="J36" t="n">
+        <v>3.2056</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>1.6499</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.1888</v>
+      </c>
+      <c r="N36" t="n">
+        <v>13.2292</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0.4635</v>
+      </c>
+      <c r="P36" t="n">
+        <v>3.9156</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>1.2303</v>
+      </c>
+      <c r="R36" t="n">
+        <v>9.9025</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0.6067</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1.0001</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2.7905</v>
+      </c>
+      <c r="V36" t="n">
+        <v>2.6451</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="n">
+        <v>43465</v>
+      </c>
+      <c r="B37" t="n">
+        <v>43.3163</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1.754</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.7069</v>
+      </c>
+      <c r="F37" t="n">
+        <v>40.8552</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.5847</v>
+      </c>
+      <c r="I37" t="n">
+        <v>6.1857</v>
+      </c>
+      <c r="J37" t="n">
+        <v>3.549</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>1.5445</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.1875</v>
+      </c>
+      <c r="N37" t="n">
+        <v>10.9457</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0.3181</v>
+      </c>
+      <c r="P37" t="n">
+        <v>6.8984</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>1.1918</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7.5475</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0.6385</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0.9431</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2.1023</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.5522</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="n">
+        <v>43555</v>
+      </c>
+      <c r="B38" t="n">
+        <v>44.5582</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1.8755</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.731</v>
+      </c>
+      <c r="F38" t="n">
+        <v>41.9516</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>-0.6645</v>
+      </c>
+      <c r="I38" t="n">
+        <v>9.2698</v>
+      </c>
+      <c r="J38" t="n">
+        <v>3.1369</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>1.6299</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0.1475</v>
+      </c>
+      <c r="N38" t="n">
+        <v>11.7107</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0.2223</v>
+      </c>
+      <c r="P38" t="n">
+        <v>7.1653</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0.9826</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7.9757</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0.6516</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0.8304</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.4524</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0.8984</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="n">
+        <v>43646</v>
+      </c>
+      <c r="B39" t="n">
+        <v>47.4524</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D39" t="n">
+        <v>2.0351</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.7798</v>
+      </c>
+      <c r="F39" t="n">
+        <v>44.6126</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>-0.5869</v>
+      </c>
+      <c r="I39" t="n">
+        <v>9.603199999999999</v>
+      </c>
+      <c r="J39" t="n">
+        <v>2.5761</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>1.6908</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.1949</v>
+      </c>
+      <c r="N39" t="n">
+        <v>12.3513</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0.3716</v>
+      </c>
+      <c r="P39" t="n">
+        <v>4.6887</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>1.1791</v>
+      </c>
+      <c r="R39" t="n">
+        <v>8.492900000000001</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0.6983</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0.9812</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2.2519</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.7195</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="n">
+        <v>43738</v>
+      </c>
+      <c r="B40" t="n">
+        <v>53.7214</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="D40" t="n">
+        <v>2.033</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.7245</v>
+      </c>
+      <c r="F40" t="n">
+        <v>50.9629</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>-0.0912</v>
+      </c>
+      <c r="I40" t="n">
+        <v>11.4292</v>
+      </c>
+      <c r="J40" t="n">
+        <v>3.3147</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>1.7335</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.2441</v>
+      </c>
+      <c r="N40" t="n">
+        <v>12.8976</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0.4554</v>
+      </c>
+      <c r="P40" t="n">
+        <v>4.2872</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>1.2727</v>
+      </c>
+      <c r="R40" t="n">
+        <v>8.881</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0.7597</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1.0454</v>
+      </c>
+      <c r="U40" t="n">
+        <v>2.7656</v>
+      </c>
+      <c r="V40" t="n">
+        <v>2.6352</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="n">
+        <v>43830</v>
+      </c>
+      <c r="B41" t="n">
+        <v>48.8807</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.0354</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1.4917</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.5629</v>
+      </c>
+      <c r="F41" t="n">
+        <v>46.7907</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.6464</v>
+      </c>
+      <c r="I41" t="n">
+        <v>6.7233</v>
+      </c>
+      <c r="J41" t="n">
+        <v>3.5363</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>1.4873</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.1782</v>
+      </c>
+      <c r="N41" t="n">
+        <v>14.0732</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0.3005</v>
+      </c>
+      <c r="P41" t="n">
+        <v>5.5952</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>1.2434</v>
+      </c>
+      <c r="R41" t="n">
+        <v>9.231199999999999</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0.663</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0.9688</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2.0382</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1.5811</v>
+      </c>
+      <c r="W41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="n">
+        <v>43921</v>
+      </c>
+      <c r="B42" t="n">
+        <v>46.4875</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.1965</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1.8681</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.4592</v>
+      </c>
+      <c r="F42" t="n">
+        <v>43.9637</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.7917</v>
+      </c>
+      <c r="I42" t="n">
+        <v>9.0573</v>
+      </c>
+      <c r="J42" t="n">
+        <v>3.3326</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>1.4402</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.1696</v>
+      </c>
+      <c r="N42" t="n">
+        <v>12.3044</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0.2512</v>
+      </c>
+      <c r="P42" t="n">
+        <v>4.548</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0.9865</v>
+      </c>
+      <c r="R42" t="n">
+        <v>8.447900000000001</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0.5958</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0.5586</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1.593</v>
+      </c>
+      <c r="V42" t="n">
+        <v>0.9668</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="n">
+        <v>44012</v>
+      </c>
+      <c r="B43" t="n">
+        <v>48.9499</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.7241</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1.8277</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.1962</v>
+      </c>
+      <c r="F43" t="n">
+        <v>46.2019</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="I43" t="n">
+        <v>11.6786</v>
+      </c>
+      <c r="J43" t="n">
+        <v>2.3634</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>1.1593</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0.2087</v>
+      </c>
+      <c r="N43" t="n">
+        <v>12.3872</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0.3732</v>
+      </c>
+      <c r="P43" t="n">
+        <v>4.0911</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>1.0406</v>
+      </c>
+      <c r="R43" t="n">
+        <v>8.407999999999999</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0.5603</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0.4692</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1.8313</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1.8326</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="n">
+        <v>44104</v>
+      </c>
+      <c r="B44" t="n">
+        <v>48.7334</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>1.9595</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.2018</v>
+      </c>
+      <c r="F44" t="n">
+        <v>46.5721</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>-0.6903</v>
+      </c>
+      <c r="I44" t="n">
+        <v>13.1881</v>
+      </c>
+      <c r="J44" t="n">
+        <v>3.3825</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>1.1733</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0.2537</v>
+      </c>
+      <c r="N44" t="n">
+        <v>9.7278</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0.4789</v>
+      </c>
+      <c r="P44" t="n">
+        <v>5.102</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>1.329</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6.8468</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0.7409</v>
+      </c>
+      <c r="T44" t="n">
+        <v>0.6405999999999999</v>
+      </c>
+      <c r="U44" t="n">
+        <v>2.5954</v>
+      </c>
+      <c r="V44" t="n">
+        <v>2.818</v>
+      </c>
+      <c r="W44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="n">
+        <v>44196</v>
+      </c>
+      <c r="B45" t="n">
+        <v>45.3525</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0.0723</v>
+      </c>
+      <c r="D45" t="n">
+        <v>1.7655</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.1727</v>
+      </c>
+      <c r="F45" t="n">
+        <v>43.3421</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.1735</v>
+      </c>
+      <c r="I45" t="n">
+        <v>7.2058</v>
+      </c>
+      <c r="J45" t="n">
+        <v>3.5424</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>1.1936</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0.1857</v>
+      </c>
+      <c r="N45" t="n">
+        <v>11.8109</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0.3142</v>
+      </c>
+      <c r="P45" t="n">
+        <v>5.9862</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>1.2517</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7.8556</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0.589</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1.8561</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1.5804</v>
+      </c>
+      <c r="W45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="n">
+        <v>44286</v>
+      </c>
+      <c r="B46" t="n">
+        <v>40.8657</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" t="n">
+        <v>1.614</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.2896</v>
+      </c>
+      <c r="F46" t="n">
+        <v>38.9621</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>1.1016</v>
+      </c>
+      <c r="I46" t="n">
+        <v>6.7683</v>
+      </c>
+      <c r="J46" t="n">
+        <v>3.2642</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>1.1418</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0.1635</v>
+      </c>
+      <c r="N46" t="n">
+        <v>10.37</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0.2427</v>
+      </c>
+      <c r="P46" t="n">
+        <v>4.8786</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>1.0983</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6.9417</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0.1653</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0.7752</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1.4342</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1.026</v>
+      </c>
+      <c r="W46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="n">
+        <v>44377</v>
+      </c>
+      <c r="B47" t="n">
+        <v>40.699</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" t="n">
+        <v>1.6376</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.2616</v>
+      </c>
+      <c r="F47" t="n">
+        <v>38.7998</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>-0.07539999999999999</v>
+      </c>
+      <c r="I47" t="n">
+        <v>9.3604</v>
+      </c>
+      <c r="J47" t="n">
+        <v>2.5572</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>1.1783</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0.1855</v>
+      </c>
+      <c r="N47" t="n">
+        <v>8.854900000000001</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0.3162</v>
+      </c>
+      <c r="P47" t="n">
+        <v>4.1867</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>1.1594</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6.1162</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0.153</v>
+      </c>
+      <c r="T47" t="n">
+        <v>0.8519</v>
+      </c>
+      <c r="U47" t="n">
+        <v>2.0908</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1.716</v>
+      </c>
+      <c r="W47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="n">
+        <v>44469</v>
+      </c>
+      <c r="B48" t="n">
+        <v>41.0685</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" t="n">
+        <v>1.6871</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.2473</v>
+      </c>
+      <c r="F48" t="n">
+        <v>39.1341</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.264</v>
+      </c>
+      <c r="I48" t="n">
+        <v>9.617900000000001</v>
+      </c>
+      <c r="J48" t="n">
+        <v>3.1023</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>1.1532</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0.2352</v>
+      </c>
+      <c r="N48" t="n">
+        <v>7.5897</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0.4737</v>
+      </c>
+      <c r="P48" t="n">
+        <v>4.6688</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0.9255</v>
+      </c>
+      <c r="R48" t="n">
+        <v>5.4544</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0.6031</v>
+      </c>
+      <c r="T48" t="n">
+        <v>0.8725000000000001</v>
+      </c>
+      <c r="U48" t="n">
+        <v>2.5417</v>
+      </c>
+      <c r="V48" t="n">
+        <v>2.8153</v>
+      </c>
+      <c r="W48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="n">
+        <v>44561</v>
+      </c>
+      <c r="B49" t="n">
+        <v>43.0301</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0.2333</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1.9104</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.2573</v>
+      </c>
+      <c r="F49" t="n">
+        <v>40.6292</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>2.799</v>
+      </c>
+      <c r="I49" t="n">
+        <v>4.7461</v>
+      </c>
+      <c r="J49" t="n">
+        <v>3.508</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>1.1606</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0.1789</v>
+      </c>
+      <c r="N49" t="n">
+        <v>11.0135</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0.274</v>
+      </c>
+      <c r="P49" t="n">
+        <v>5.6596</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0.5613</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7.4661</v>
+      </c>
+      <c r="S49" t="n">
+        <v>0.4934</v>
+      </c>
+      <c r="T49" t="n">
+        <v>0.8343</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1.5987</v>
+      </c>
+      <c r="V49" t="n">
+        <v>1.6335</v>
+      </c>
+      <c r="W49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="n">
+        <v>44651</v>
+      </c>
+      <c r="B50" t="n">
+        <v>41.5058</v>
+      </c>
+      <c r="C50" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="D50" t="n">
+        <v>1.9425</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.2421</v>
+      </c>
+      <c r="F50" t="n">
+        <v>39.3193</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>-0.3783</v>
+      </c>
+      <c r="I50" t="n">
+        <v>8.939</v>
+      </c>
+      <c r="J50" t="n">
+        <v>3.3152</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="n">
+        <v>1.1006</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0.1827</v>
+      </c>
+      <c r="N50" t="n">
+        <v>10.7558</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0.1975</v>
+      </c>
+      <c r="P50" t="n">
+        <v>4.796</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0.6633</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7.2774</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0.6152</v>
+      </c>
+      <c r="T50" t="n">
+        <v>0.7895</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1.274</v>
+      </c>
+      <c r="V50" t="n">
+        <v>0.9746</v>
+      </c>
+      <c r="W50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="n">
+        <v>44742</v>
+      </c>
+      <c r="B51" t="n">
+        <v>36.9326</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" t="n">
+        <v>1.833</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.2229</v>
+      </c>
+      <c r="F51" t="n">
+        <v>34.8767</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>-2.422</v>
+      </c>
+      <c r="I51" t="n">
+        <v>11.0062</v>
+      </c>
+      <c r="J51" t="n">
+        <v>2.9342</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0.9536</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0.1599</v>
+      </c>
+      <c r="N51" t="n">
+        <v>7.2054</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P51" t="n">
+        <v>4.6134</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0.6179</v>
+      </c>
+      <c r="R51" t="n">
+        <v>5.0293</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0.647</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0.9107</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1.8741</v>
+      </c>
+      <c r="V51" t="n">
+        <v>1.6621</v>
+      </c>
+      <c r="W51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="n">
+        <v>44834</v>
+      </c>
+      <c r="B52" t="n">
+        <v>37.1878</v>
+      </c>
+      <c r="C52" t="n">
+        <v>0.0051</v>
+      </c>
+      <c r="D52" t="n">
+        <v>1.8316</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.1982</v>
+      </c>
+      <c r="F52" t="n">
+        <v>35.1529</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="I52" t="n">
+        <v>7.5827</v>
+      </c>
+      <c r="J52" t="n">
+        <v>2.8421</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0.901</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0.2117</v>
+      </c>
+      <c r="N52" t="n">
+        <v>6.2656</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="P52" t="n">
+        <v>4.3981</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>0.7871</v>
+      </c>
+      <c r="R52" t="n">
+        <v>4.5855</v>
+      </c>
+      <c r="S52" t="n">
+        <v>0.6025</v>
+      </c>
+      <c r="T52" t="n">
+        <v>0.9059</v>
+      </c>
+      <c r="U52" t="n">
+        <v>2.4306</v>
+      </c>
+      <c r="V52" t="n">
+        <v>2.5812</v>
+      </c>
+      <c r="W52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="n">
+        <v>44926</v>
+      </c>
+      <c r="B53" t="n">
+        <v>35.5811</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" t="n">
+        <v>1.4739</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.2353</v>
+      </c>
+      <c r="F53" t="n">
+        <v>33.8719</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>-3.9054</v>
+      </c>
+      <c r="I53" t="n">
+        <v>2.0918</v>
+      </c>
+      <c r="J53" t="n">
+        <v>3.2786</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0.8197</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0.1709</v>
+      </c>
+      <c r="N53" t="n">
+        <v>11.0372</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0.2541</v>
+      </c>
+      <c r="P53" t="n">
+        <v>3.4073</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>0.8474</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6.8801</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0.5775</v>
+      </c>
+      <c r="T53" t="n">
+        <v>0.8898</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1.869</v>
+      </c>
+      <c r="V53" t="n">
+        <v>1.5718</v>
+      </c>
+      <c r="W53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="n">
+        <v>45016</v>
+      </c>
+      <c r="B54" t="n">
+        <v>39.8363</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="D54" t="n">
+        <v>1.6963</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.2826</v>
+      </c>
+      <c r="F54" t="n">
+        <v>37.8433</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>-0.0825</v>
+      </c>
+      <c r="I54" t="n">
+        <v>7.6181</v>
+      </c>
+      <c r="J54" t="n">
+        <v>3.3409</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0.7315</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0.1431</v>
+      </c>
+      <c r="N54" t="n">
+        <v>11.1361</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0.1989</v>
+      </c>
+      <c r="P54" t="n">
+        <v>4.8846</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>0.6616</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6.8113</v>
+      </c>
+      <c r="S54" t="n">
+        <v>0.5764</v>
+      </c>
+      <c r="T54" t="n">
+        <v>0.7047</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1.4267</v>
+      </c>
+      <c r="V54" t="n">
+        <v>1.054</v>
+      </c>
+      <c r="W54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="n">
+        <v>45107</v>
+      </c>
+      <c r="B55" t="n">
+        <v>40.132</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0.0432</v>
+      </c>
+      <c r="D55" t="n">
+        <v>1.7461</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.2006</v>
+      </c>
+      <c r="F55" t="n">
+        <v>38.1422</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>1.1932</v>
+      </c>
+      <c r="I55" t="n">
+        <v>6.3837</v>
+      </c>
+      <c r="J55" t="n">
+        <v>2.3518</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0.8853</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0.1681</v>
+      </c>
+      <c r="N55" t="n">
+        <v>11.1039</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0.3131</v>
+      </c>
+      <c r="P55" t="n">
+        <v>4.0124</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>0.821</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6.8429</v>
+      </c>
+      <c r="S55" t="n">
+        <v>0.5883</v>
+      </c>
+      <c r="T55" t="n">
+        <v>0.7188</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1.9757</v>
+      </c>
+      <c r="V55" t="n">
+        <v>1.7538</v>
+      </c>
+      <c r="W55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="n">
+        <v>45199</v>
+      </c>
+      <c r="B56" t="n">
+        <v>40.3103</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" t="n">
+        <v>1.7766</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.2361</v>
+      </c>
+      <c r="F56" t="n">
+        <v>38.2976</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>-1.0439</v>
+      </c>
+      <c r="I56" t="n">
+        <v>13.4095</v>
+      </c>
+      <c r="J56" t="n">
+        <v>2.2677</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0.9056</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0.1415</v>
+      </c>
+      <c r="N56" t="n">
+        <v>6.6875</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0.3067</v>
+      </c>
+      <c r="P56" t="n">
+        <v>4.9744</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>0.5137</v>
+      </c>
+      <c r="R56" t="n">
+        <v>4.547</v>
+      </c>
+      <c r="S56" t="n">
+        <v>0.5780999999999999</v>
+      </c>
+      <c r="T56" t="n">
+        <v>0.7735</v>
+      </c>
+      <c r="U56" t="n">
+        <v>2.4951</v>
+      </c>
+      <c r="V56" t="n">
+        <v>2.7633</v>
+      </c>
+      <c r="W56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="n">
+        <v>45291</v>
+      </c>
+      <c r="B57" t="n">
+        <v>35.2398</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" t="n">
+        <v>1.2354</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.1897</v>
+      </c>
+      <c r="F57" t="n">
+        <v>33.8146</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>-0.9633</v>
+      </c>
+      <c r="I57" t="n">
+        <v>5.2609</v>
+      </c>
+      <c r="J57" t="n">
+        <v>2.3467</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0.8475</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0.0998</v>
+      </c>
+      <c r="N57" t="n">
+        <v>9.696099999999999</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0.2275</v>
+      </c>
+      <c r="P57" t="n">
+        <v>6.4514</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0.7057</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6.2215</v>
+      </c>
+      <c r="S57" t="n">
+        <v>0.5569</v>
+      </c>
+      <c r="T57" t="n">
+        <v>0.7754</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1.8266</v>
+      </c>
+      <c r="V57" t="n">
+        <v>1.6334</v>
+      </c>
+      <c r="W57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="n">
+        <v>45382</v>
+      </c>
+      <c r="B58" t="n">
+        <v>33.9086</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" t="n">
+        <v>1.6695</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.1711</v>
+      </c>
+      <c r="F58" t="n">
+        <v>32.068</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>-0.7711</v>
+      </c>
+      <c r="I58" t="n">
+        <v>8.6853</v>
+      </c>
+      <c r="J58" t="n">
+        <v>2.2614</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0.968</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0.1396</v>
+      </c>
+      <c r="N58" t="n">
+        <v>7.472</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0.2162</v>
+      </c>
+      <c r="P58" t="n">
+        <v>5.2293</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>0.6652</v>
+      </c>
+      <c r="R58" t="n">
+        <v>4.7192</v>
+      </c>
+      <c r="S58" t="n">
+        <v>0.5626</v>
+      </c>
+      <c r="T58" t="n">
+        <v>0.7233000000000001</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1.4204</v>
+      </c>
+      <c r="V58" t="n">
+        <v>1.1531</v>
+      </c>
+      <c r="W58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="n">
+        <v>45473</v>
+      </c>
+      <c r="B59" t="n">
+        <v>32.9149</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" t="n">
+        <v>1.5958</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.2752</v>
+      </c>
+      <c r="F59" t="n">
+        <v>31.044</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="n">
+        <v>-0.6158</v>
+      </c>
+      <c r="I59" t="n">
+        <v>8.7836</v>
+      </c>
+      <c r="J59" t="n">
+        <v>2.3074</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
+        <v>1.0953</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="N59" t="n">
+        <v>5.5315</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0.2843</v>
+      </c>
+      <c r="P59" t="n">
+        <v>4.559</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>0.6781</v>
+      </c>
+      <c r="R59" t="n">
+        <v>3.6844</v>
+      </c>
+      <c r="S59" t="n">
+        <v>0.653</v>
+      </c>
+      <c r="T59" t="n">
+        <v>0.8459</v>
+      </c>
+      <c r="U59" t="n">
+        <v>2.1067</v>
+      </c>
+      <c r="V59" t="n">
+        <v>1.9379</v>
+      </c>
+      <c r="W59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="n">
+        <v>45565</v>
+      </c>
+      <c r="B60" t="n">
+        <v>32.1622</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1.5412</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.3959</v>
+      </c>
+      <c r="F60" t="n">
+        <v>30.2251</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.7935</v>
+      </c>
+      <c r="I60" t="n">
+        <v>9.1503</v>
+      </c>
+      <c r="J60" t="n">
+        <v>2.2639</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0.9663</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0.1395</v>
+      </c>
+      <c r="N60" t="n">
+        <v>2.8507</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0.4028</v>
+      </c>
+      <c r="P60" t="n">
+        <v>5.0192</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>0.4505</v>
+      </c>
+      <c r="R60" t="n">
+        <v>2.0102</v>
+      </c>
+      <c r="S60" t="n">
+        <v>0.6808999999999999</v>
+      </c>
+      <c r="T60" t="n">
+        <v>0.8746</v>
+      </c>
+      <c r="U60" t="n">
+        <v>2.4244</v>
+      </c>
+      <c r="V60" t="n">
+        <v>2.6332</v>
+      </c>
+      <c r="W60" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="n">
+        <v>45657</v>
+      </c>
+      <c r="B61" t="n">
+        <v>27.9034</v>
+      </c>
+      <c r="C61" t="n">
+        <v>0</v>
+      </c>
+      <c r="D61" t="n">
+        <v>1.3096</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.2953</v>
+      </c>
+      <c r="F61" t="n">
+        <v>26.2984</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="n">
+        <v>2.3368</v>
+      </c>
+      <c r="I61" t="n">
+        <v>3.0137</v>
+      </c>
+      <c r="J61" t="n">
+        <v>2.211</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0.1231</v>
+      </c>
+      <c r="N61" t="n">
+        <v>4.6377</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0.2716</v>
+      </c>
+      <c r="P61" t="n">
+        <v>5.8665</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>0.6345</v>
+      </c>
+      <c r="R61" t="n">
+        <v>3.109</v>
+      </c>
+      <c r="S61" t="n">
+        <v>0.5371</v>
+      </c>
+      <c r="T61" t="n">
+        <v>0.7712</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1.8053</v>
+      </c>
+      <c r="V61" t="n">
+        <v>1.5519</v>
+      </c>
+      <c r="W61" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="n">
+        <v>45747</v>
+      </c>
+      <c r="B62" t="n">
+        <v>27.6733</v>
+      </c>
+      <c r="C62" t="n">
+        <v>0</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1.3674</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.3769</v>
+      </c>
+      <c r="F62" t="n">
+        <v>25.929</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="n">
+        <v>-2.4564</v>
+      </c>
+      <c r="I62" t="n">
+        <v>8.8843</v>
+      </c>
+      <c r="J62" t="n">
+        <v>2.2175</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0.9859</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0.1177</v>
+      </c>
+      <c r="N62" t="n">
+        <v>5.0315</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0.2039</v>
+      </c>
+      <c r="P62" t="n">
+        <v>5.0682</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>0.6442</v>
+      </c>
+      <c r="R62" t="n">
+        <v>3.2858</v>
+      </c>
+      <c r="S62" t="n">
+        <v>0.5446</v>
+      </c>
+      <c r="T62" t="n">
+        <v>0.7176</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1.4231</v>
+      </c>
+      <c r="V62" t="n">
+        <v>1.0386</v>
+      </c>
+      <c r="W62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="n">
+        <v>45838</v>
+      </c>
+      <c r="B63" t="n">
+        <v>27.3417</v>
+      </c>
+      <c r="C63" t="n">
+        <v>0.0448</v>
+      </c>
+      <c r="D63" t="n">
+        <v>1.3006</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.2677</v>
+      </c>
+      <c r="F63" t="n">
+        <v>25.7286</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.9331</v>
+      </c>
+      <c r="I63" t="n">
+        <v>8.7065</v>
+      </c>
+      <c r="J63" t="n">
+        <v>2.1437</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0.9054</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0.1206</v>
+      </c>
+      <c r="N63" t="n">
+        <v>2.3419</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="P63" t="n">
+        <v>4.359</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>0.706</v>
+      </c>
+      <c r="R63" t="n">
+        <v>1.8002</v>
+      </c>
+      <c r="S63" t="n">
+        <v>0.5933</v>
+      </c>
+      <c r="T63" t="n">
+        <v>0.7875</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1.6978</v>
+      </c>
+      <c r="V63" t="n">
+        <v>1.6161</v>
+      </c>
+      <c r="W63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="n">
+        <v>45930</v>
+      </c>
+      <c r="B64" t="n">
+        <v>27.0764</v>
+      </c>
+      <c r="C64" t="n">
+        <v>0.0439</v>
+      </c>
+      <c r="D64" t="n">
+        <v>1.2304</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.3041</v>
+      </c>
+      <c r="F64" t="n">
+        <v>25.498</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
+        <v>-2.3557</v>
+      </c>
+      <c r="I64" t="n">
+        <v>6.9756</v>
+      </c>
+      <c r="J64" t="n">
+        <v>2.0034</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0.9938</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0.1326</v>
+      </c>
+      <c r="N64" t="n">
+        <v>4.1775</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0.4202</v>
+      </c>
+      <c r="P64" t="n">
+        <v>5.1208</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>0.4513</v>
+      </c>
+      <c r="R64" t="n">
+        <v>3.0104</v>
+      </c>
+      <c r="S64" t="n">
+        <v>0.6102</v>
+      </c>
+      <c r="T64" t="n">
+        <v>0.7665</v>
+      </c>
+      <c r="U64" t="n">
+        <v>2.4185</v>
+      </c>
+      <c r="V64" t="n">
+        <v>2.4707</v>
+      </c>
+      <c r="W64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B65" t="n">
+        <v>26.7693</v>
+      </c>
+      <c r="C65" t="n">
+        <v>0.0098</v>
+      </c>
+      <c r="D65" t="n">
+        <v>1.1788</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0.2956</v>
+      </c>
+      <c r="F65" t="n">
+        <v>25.2851</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" t="n">
+        <v>3.2977</v>
+      </c>
+      <c r="I65" t="n">
+        <v>1.2597</v>
+      </c>
+      <c r="J65" t="n">
+        <v>1.8973</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0.975</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0.1224</v>
+      </c>
+      <c r="N65" t="n">
+        <v>5.3483</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0.2555</v>
+      </c>
+      <c r="P65" t="n">
+        <v>5.9511</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>0.5452</v>
+      </c>
+      <c r="R65" t="n">
+        <v>3.3498</v>
+      </c>
+      <c r="S65" t="n">
+        <v>0.551</v>
+      </c>
+      <c r="T65" t="n">
+        <v>0.7251</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1.4168</v>
+      </c>
+      <c r="V65" t="n">
+        <v>1.4057</v>
+      </c>
+      <c r="W65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B66" t="n">
+        <v>22.9596</v>
+      </c>
+      <c r="C66" t="n">
+        <v>0.0529</v>
+      </c>
+      <c r="D66" t="n">
+        <v>0.842</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0.2439</v>
+      </c>
+      <c r="F66" t="n">
+        <v>21.8207</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0.5709</v>
+      </c>
+      <c r="I66" t="n">
+        <v>2.875</v>
+      </c>
+      <c r="J66" t="n">
+        <v>1.8074</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0.7927999999999999</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0.1163</v>
+      </c>
+      <c r="N66" t="n">
+        <v>4.7073</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0.1814</v>
+      </c>
+      <c r="P66" t="n">
+        <v>4.9023</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>0.4908</v>
+      </c>
+      <c r="R66" t="n">
+        <v>3.6009</v>
+      </c>
+      <c r="S66" t="n">
+        <v>0.5611</v>
+      </c>
+      <c r="T66" t="n">
+        <v>0.6943</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1.0867</v>
+      </c>
+      <c r="V66" t="n">
+        <v>0.9808</v>
+      </c>
+      <c r="W66" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B67" t="n">
+        <v>21.8081</v>
+      </c>
+      <c r="C67" t="n">
+        <v>0.0575</v>
+      </c>
+      <c r="D67" t="n">
+        <v>0.915</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0.1294</v>
+      </c>
+      <c r="F67" t="n">
+        <v>20.7063</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0.2786</v>
+      </c>
+      <c r="I67" t="n">
+        <v>5.3746</v>
+      </c>
+      <c r="J67" t="n">
+        <v>1.7914</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0.8295</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0.1191</v>
+      </c>
+      <c r="N67" t="n">
+        <v>2.1376</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0.2492</v>
+      </c>
+      <c r="P67" t="n">
+        <v>3.8266</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>0.5246</v>
+      </c>
+      <c r="R67" t="n">
+        <v>1.6638</v>
+      </c>
+      <c r="S67" t="n">
+        <v>0.6042999999999999</v>
+      </c>
+      <c r="T67" t="n">
+        <v>0.7953</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1.3868</v>
+      </c>
+      <c r="V67" t="n">
+        <v>1.5846</v>
+      </c>
+      <c r="W67" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/output/Data and Chart Outputs/nz_gas.xlsx
+++ b/output/Data and Chart Outputs/nz_gas.xlsx
@@ -616,90 +616,6 @@
             </numRef>
           </val>
         </ser>
-        <ser>
-          <idx val="5"/>
-          <order val="5"/>
-          <tx>
-            <strRef>
-              <f>'Chart - Demand'!G1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill>
-              <a:srgbClr val="008300"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Chart - Demand'!$A$2:$A$23</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Chart - Demand'!$G$2:$G$23</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="6"/>
-          <order val="6"/>
-          <tx>
-            <strRef>
-              <f>'Chart - Demand'!H1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill>
-              <a:srgbClr val="4A3AA7"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Chart - Demand'!$A$2:$A$23</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Chart - Demand'!$H$2:$H$23</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="7"/>
-          <order val="7"/>
-          <tx>
-            <strRef>
-              <f>'Chart - Demand'!I1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill>
-              <a:srgbClr val="E34948"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Chart - Demand'!$A$2:$A$23</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Chart - Demand'!$I$2:$I$23</f>
-            </numRef>
-          </val>
-        </ser>
         <gapWidth val="30"/>
         <overlap val="100"/>
         <axId val="10"/>
@@ -842,7 +758,7 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>10</col>
+      <col>7</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -2574,7 +2490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2588,42 +2504,27 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Gross Production</t>
+          <t>Power (incl. cogeneration)</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Gas Reinjected</t>
+          <t>Petrochemicals (non-energy: methanol, urea)</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>LPG extracted</t>
+          <t>Industry</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Gas Flared</t>
+          <t>Commercial &amp; residential</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Net Production</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Manufactured Production</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Stock Change</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Electricity Generation</t>
+          <t>Transport &amp; other transformation</t>
         </is>
       </c>
     </row>
@@ -2632,28 +2533,19 @@
         <v>44286</v>
       </c>
       <c r="B2" t="n">
-        <v>40.8657</v>
+        <v>10.0325</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>10.37</v>
       </c>
       <c r="D2" t="n">
-        <v>1.614</v>
+        <v>14.1018</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2896</v>
+        <v>2.4602</v>
       </c>
       <c r="F2" t="n">
-        <v>38.9621</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1.1016</v>
-      </c>
-      <c r="I2" t="n">
-        <v>6.7683</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -2661,28 +2553,19 @@
         <v>44377</v>
       </c>
       <c r="B3" t="n">
-        <v>40.699</v>
+        <v>11.9176</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>8.854900000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6376</v>
+        <v>12.7834</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2616</v>
+        <v>3.8068</v>
       </c>
       <c r="F3" t="n">
-        <v>38.7998</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-0.07539999999999999</v>
-      </c>
-      <c r="I3" t="n">
-        <v>9.3604</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -2690,28 +2573,19 @@
         <v>44469</v>
       </c>
       <c r="B4" t="n">
-        <v>41.0685</v>
+        <v>12.7202</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>7.5897</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6871</v>
+        <v>12.998</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2473</v>
+        <v>5.357</v>
       </c>
       <c r="F4" t="n">
-        <v>39.1341</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.264</v>
-      </c>
-      <c r="I4" t="n">
-        <v>9.617900000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -2719,28 +2593,19 @@
         <v>44561</v>
       </c>
       <c r="B5" t="n">
-        <v>43.0301</v>
+        <v>8.254100000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2333</v>
+        <v>11.0135</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9104</v>
+        <v>15.2887</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2573</v>
+        <v>3.2322</v>
       </c>
       <c r="F5" t="n">
-        <v>40.6292</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2.799</v>
-      </c>
-      <c r="I5" t="n">
-        <v>4.7461</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -2748,28 +2613,19 @@
         <v>44651</v>
       </c>
       <c r="B6" t="n">
-        <v>41.5058</v>
+        <v>12.2542</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002</v>
+        <v>10.7558</v>
       </c>
       <c r="D6" t="n">
-        <v>1.9425</v>
+        <v>14.3389</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2421</v>
+        <v>2.2486</v>
       </c>
       <c r="F6" t="n">
-        <v>39.3193</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-0.3783</v>
-      </c>
-      <c r="I6" t="n">
-        <v>8.939</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -2777,28 +2633,19 @@
         <v>44742</v>
       </c>
       <c r="B7" t="n">
-        <v>36.9326</v>
+        <v>13.9404</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>7.2054</v>
       </c>
       <c r="D7" t="n">
-        <v>1.833</v>
+        <v>12.0683</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2229</v>
+        <v>3.5362</v>
       </c>
       <c r="F7" t="n">
-        <v>34.8767</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-2.422</v>
-      </c>
-      <c r="I7" t="n">
-        <v>11.0062</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -2806,28 +2653,19 @@
         <v>44834</v>
       </c>
       <c r="B8" t="n">
-        <v>37.1878</v>
+        <v>10.4248</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0051</v>
+        <v>6.2656</v>
       </c>
       <c r="D8" t="n">
-        <v>1.8316</v>
+        <v>11.5841</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1982</v>
+        <v>5.0118</v>
       </c>
       <c r="F8" t="n">
-        <v>35.1529</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="I8" t="n">
-        <v>7.5827</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -2835,28 +2673,19 @@
         <v>44926</v>
       </c>
       <c r="B9" t="n">
-        <v>35.5811</v>
+        <v>5.3704</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>11.0372</v>
       </c>
       <c r="D9" t="n">
-        <v>1.4739</v>
+        <v>12.8562</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2353</v>
+        <v>3.4408</v>
       </c>
       <c r="F9" t="n">
-        <v>33.8719</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-3.9054</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2.0918</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -2864,28 +2693,19 @@
         <v>45016</v>
       </c>
       <c r="B10" t="n">
-        <v>39.8363</v>
+        <v>10.959</v>
       </c>
       <c r="C10" t="n">
-        <v>0.014</v>
+        <v>11.1361</v>
       </c>
       <c r="D10" t="n">
-        <v>1.6963</v>
+        <v>13.8375</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2826</v>
+        <v>2.4807</v>
       </c>
       <c r="F10" t="n">
-        <v>37.8433</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-0.0825</v>
-      </c>
-      <c r="I10" t="n">
-        <v>7.6181</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -2893,28 +2713,19 @@
         <v>45107</v>
       </c>
       <c r="B11" t="n">
-        <v>40.132</v>
+        <v>8.7355</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0432</v>
+        <v>11.1039</v>
       </c>
       <c r="D11" t="n">
-        <v>1.7461</v>
+        <v>13.2965</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2006</v>
+        <v>3.7295</v>
       </c>
       <c r="F11" t="n">
-        <v>38.1422</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>1.1932</v>
-      </c>
-      <c r="I11" t="n">
-        <v>6.3837</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -2922,28 +2733,19 @@
         <v>45199</v>
       </c>
       <c r="B12" t="n">
-        <v>40.3103</v>
+        <v>15.6772</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>6.6875</v>
       </c>
       <c r="D12" t="n">
-        <v>1.7766</v>
+        <v>11.6934</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2361</v>
+        <v>5.2584</v>
       </c>
       <c r="F12" t="n">
-        <v>38.2976</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-1.0439</v>
-      </c>
-      <c r="I12" t="n">
-        <v>13.4095</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -2951,28 +2753,19 @@
         <v>45291</v>
       </c>
       <c r="B13" t="n">
-        <v>35.2398</v>
+        <v>7.6076</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>9.696099999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>1.2354</v>
+        <v>14.9384</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1897</v>
+        <v>3.46</v>
       </c>
       <c r="F13" t="n">
-        <v>33.8146</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-0.9633</v>
-      </c>
-      <c r="I13" t="n">
-        <v>5.2609</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -2980,28 +2773,19 @@
         <v>45382</v>
       </c>
       <c r="B14" t="n">
-        <v>33.9086</v>
+        <v>10.9467</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>7.472</v>
       </c>
       <c r="D14" t="n">
-        <v>1.6695</v>
+        <v>12.1158</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1711</v>
+        <v>2.5735</v>
       </c>
       <c r="F14" t="n">
-        <v>32.068</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-0.7711</v>
-      </c>
-      <c r="I14" t="n">
-        <v>8.6853</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -3009,28 +2793,19 @@
         <v>45473</v>
       </c>
       <c r="B15" t="n">
-        <v>32.9149</v>
+        <v>11.091</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>5.5315</v>
       </c>
       <c r="D15" t="n">
-        <v>1.5958</v>
+        <v>10.7047</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2752</v>
+        <v>4.0446</v>
       </c>
       <c r="F15" t="n">
-        <v>31.044</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-0.6158</v>
-      </c>
-      <c r="I15" t="n">
-        <v>8.7836</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3038,28 +2813,19 @@
         <v>45565</v>
       </c>
       <c r="B16" t="n">
-        <v>32.1622</v>
+        <v>11.4142</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>2.8507</v>
       </c>
       <c r="D16" t="n">
-        <v>1.5412</v>
+        <v>9.438199999999998</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3959</v>
+        <v>5.0576</v>
       </c>
       <c r="F16" t="n">
-        <v>30.2251</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.7935</v>
-      </c>
-      <c r="I16" t="n">
-        <v>9.1503</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3067,28 +2833,19 @@
         <v>45657</v>
       </c>
       <c r="B17" t="n">
-        <v>27.9034</v>
+        <v>5.2247</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>4.6377</v>
       </c>
       <c r="D17" t="n">
-        <v>1.3096</v>
+        <v>11.1899</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2953</v>
+        <v>3.3572</v>
       </c>
       <c r="F17" t="n">
-        <v>26.2984</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>2.3368</v>
-      </c>
-      <c r="I17" t="n">
-        <v>3.0137</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3096,28 +2853,19 @@
         <v>45747</v>
       </c>
       <c r="B18" t="n">
-        <v>27.6733</v>
+        <v>11.1018</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>5.0315</v>
       </c>
       <c r="D18" t="n">
-        <v>1.3674</v>
+        <v>10.4643</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3769</v>
+        <v>2.4617</v>
       </c>
       <c r="F18" t="n">
-        <v>25.929</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-2.4564</v>
-      </c>
-      <c r="I18" t="n">
-        <v>8.8843</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3125,28 +2873,19 @@
         <v>45838</v>
       </c>
       <c r="B19" t="n">
-        <v>27.3417</v>
+        <v>10.8502</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0448</v>
+        <v>2.3419</v>
       </c>
       <c r="D19" t="n">
-        <v>1.3006</v>
+        <v>8.555000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2677</v>
+        <v>3.3139</v>
       </c>
       <c r="F19" t="n">
-        <v>25.7286</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.9331</v>
-      </c>
-      <c r="I19" t="n">
-        <v>8.7065</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -3154,28 +2893,19 @@
         <v>45930</v>
       </c>
       <c r="B20" t="n">
-        <v>27.0764</v>
+        <v>8.978999999999999</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0439</v>
+        <v>4.1775</v>
       </c>
       <c r="D20" t="n">
-        <v>1.2304</v>
+        <v>10.3794</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3041</v>
+        <v>4.8892</v>
       </c>
       <c r="F20" t="n">
-        <v>25.498</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-2.3557</v>
-      </c>
-      <c r="I20" t="n">
-        <v>6.9756</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -3183,28 +2913,19 @@
         <v>46022</v>
       </c>
       <c r="B21" t="n">
-        <v>26.7693</v>
+        <v>3.157</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0098</v>
+        <v>5.3483</v>
       </c>
       <c r="D21" t="n">
-        <v>1.1788</v>
+        <v>11.3777</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2956</v>
+        <v>2.8225</v>
       </c>
       <c r="F21" t="n">
-        <v>25.2851</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>3.2977</v>
-      </c>
-      <c r="I21" t="n">
-        <v>1.2597</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -3212,28 +2933,19 @@
         <v>46112</v>
       </c>
       <c r="B22" t="n">
-        <v>22.9596</v>
+        <v>4.682399999999999</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0529</v>
+        <v>4.7073</v>
       </c>
       <c r="D22" t="n">
-        <v>0.842</v>
+        <v>10.4308</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2439</v>
+        <v>2.0675</v>
       </c>
       <c r="F22" t="n">
-        <v>21.8207</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.5709</v>
-      </c>
-      <c r="I22" t="n">
-        <v>2.875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -3241,28 +2953,19 @@
         <v>46203</v>
       </c>
       <c r="B23" t="n">
-        <v>21.8081</v>
+        <v>7.166</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0575</v>
+        <v>2.1376</v>
       </c>
       <c r="D23" t="n">
-        <v>0.915</v>
+        <v>7.663800000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1294</v>
+        <v>2.9714</v>
       </c>
       <c r="F23" t="n">
-        <v>20.7063</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.2786</v>
-      </c>
-      <c r="I23" t="n">
-        <v>5.3746</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/output/Data and Chart Outputs/nz_gas.xlsx
+++ b/output/Data and Chart Outputs/nz_gas.xlsx
@@ -23,8 +23,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="mmm/yy"/>
+    <numFmt numFmtId="165" formatCode="mmm/yy"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,12 +64,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -288,7 +289,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>PJ per month</a:t>
+                  <a:t>MMcf/d (1 TJ = 0.914 MMcf), monthly average</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -423,7 +424,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>PJ per month</a:t>
+                  <a:t>MMcf/d (1 TJ = 0.914 MMcf), monthly average</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -666,7 +667,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>PJ per quarter</a:t>
+                  <a:t>MMcf/d (1 TJ = 0.914 MMcf), quarterly average</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -1104,7 +1105,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -1119,7 +1119,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
@@ -1176,740 +1175,740 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
-        <v>14.5242</v>
+        <v>428.2275579177153</v>
       </c>
       <c r="C2" t="n">
-        <v>13.8371</v>
+        <v>407.969288612331</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
-        <v>12.8922</v>
+        <v>420.83619798039</v>
       </c>
       <c r="C3" t="n">
-        <v>12.3164</v>
+        <v>402.0405321671766</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
-        <v>13.4493</v>
+        <v>396.5354990087391</v>
       </c>
       <c r="C4" t="n">
-        <v>12.8086</v>
+        <v>377.6452746688181</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
-        <v>13.3347</v>
+        <v>406.2618859409952</v>
       </c>
       <c r="C5" t="n">
-        <v>12.6665</v>
+        <v>385.9041581941563</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="5" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
-        <v>13.9623</v>
+        <v>411.6606513208656</v>
       </c>
       <c r="C6" t="n">
-        <v>13.3204</v>
+        <v>392.7350465076998</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="5" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
-        <v>13.402</v>
+        <v>408.3122826446203</v>
       </c>
       <c r="C7" t="n">
-        <v>12.8129</v>
+        <v>390.3644565212099</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="5" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
-        <v>14.1403</v>
+        <v>416.9087548521687</v>
       </c>
       <c r="C8" t="n">
-        <v>13.4944</v>
+        <v>397.8652151281873</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="5" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
-        <v>14.0497</v>
+        <v>414.2375291221908</v>
       </c>
       <c r="C9" t="n">
-        <v>13.3855</v>
+        <v>394.654437181227</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="5" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
-        <v>12.8785</v>
+        <v>392.3630601431684</v>
       </c>
       <c r="C10" t="n">
-        <v>12.2543</v>
+        <v>373.3458592159358</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="5" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
-        <v>14.8064</v>
+        <v>436.54786587577</v>
       </c>
       <c r="C11" t="n">
-        <v>13.9199</v>
+        <v>410.410541266218</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="5" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
-        <v>14.3216</v>
+        <v>436.3292931743915</v>
       </c>
       <c r="C12" t="n">
-        <v>13.506</v>
+        <v>411.4808005818714</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="5" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
-        <v>13.9021</v>
+        <v>409.8857309130877</v>
       </c>
       <c r="C13" t="n">
-        <v>13.2033</v>
+        <v>389.2825019935673</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="5" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
-        <v>14.0717</v>
+        <v>414.8861711316778</v>
       </c>
       <c r="C14" t="n">
-        <v>13.3318</v>
+        <v>393.0711610035249</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="5" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
-        <v>13.0572</v>
+        <v>426.2222432377366</v>
       </c>
       <c r="C15" t="n">
-        <v>12.3864</v>
+        <v>404.3255210642328</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="5" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
-        <v>14.377</v>
+        <v>423.8875531996938</v>
       </c>
       <c r="C16" t="n">
-        <v>13.6011</v>
+        <v>401.0111288741987</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="5" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
-        <v>13.8196</v>
+        <v>421.0351008234289</v>
       </c>
       <c r="C17" t="n">
-        <v>13.0745</v>
+        <v>398.3344977941417</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="5" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
-        <v>12.0292</v>
+        <v>354.6656572963591</v>
       </c>
       <c r="C18" t="n">
-        <v>11.3409</v>
+        <v>334.3720075177302</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="5" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
-        <v>11.0838</v>
+        <v>337.6847991625461</v>
       </c>
       <c r="C19" t="n">
-        <v>10.4613</v>
+        <v>318.71939131698</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="5" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
-        <v>13.0769</v>
+        <v>385.5557588117879</v>
       </c>
       <c r="C20" t="n">
-        <v>12.3453</v>
+        <v>363.9854636235779</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="5" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
-        <v>11.2827</v>
+        <v>332.6560545653604</v>
       </c>
       <c r="C21" t="n">
-        <v>10.6098</v>
+        <v>312.8164541933721</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="5" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
-        <v>12.8282</v>
+        <v>390.8305942562094</v>
       </c>
       <c r="C22" t="n">
-        <v>12.1978</v>
+        <v>371.6245009134868</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="5" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
-        <v>12.9858</v>
+        <v>382.869791217958</v>
       </c>
       <c r="C23" t="n">
-        <v>12.2942</v>
+        <v>362.4788451379061</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="5" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
-        <v>11.1765</v>
+        <v>340.5090454393074</v>
       </c>
       <c r="C24" t="n">
-        <v>10.8077</v>
+        <v>329.2729933695167</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="5" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
-        <v>11.4188</v>
+        <v>336.6687899058679</v>
       </c>
       <c r="C25" t="n">
-        <v>10.77</v>
+        <v>317.539747371545</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="5" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
-        <v>13.268</v>
+        <v>391.1900991760128</v>
       </c>
       <c r="C26" t="n">
-        <v>12.5849</v>
+        <v>371.0497647814444</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="5" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
-        <v>12.5823</v>
+        <v>410.7202257061371</v>
       </c>
       <c r="C27" t="n">
-        <v>11.9792</v>
+        <v>391.0334142230719</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="5" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
-        <v>13.9859</v>
+        <v>412.3564672946789</v>
       </c>
       <c r="C28" t="n">
-        <v>13.2791</v>
+        <v>391.5173685535267</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="5" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
-        <v>13.8058</v>
+        <v>420.6146628663706</v>
       </c>
       <c r="C29" t="n">
-        <v>13.1157</v>
+        <v>399.5897183615913</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="5" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
-        <v>13.6299</v>
+        <v>401.8602602320724</v>
       </c>
       <c r="C30" t="n">
-        <v>12.9361</v>
+        <v>381.4044499510717</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="5" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
-        <v>12.6964</v>
+        <v>386.8151071011161</v>
       </c>
       <c r="C31" t="n">
-        <v>12.0904</v>
+        <v>368.3523968129024</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="5" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
-        <v>13.4215</v>
+        <v>395.7158513785693</v>
       </c>
       <c r="C32" t="n">
-        <v>12.7509</v>
+        <v>375.9440635803002</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="5" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
-        <v>13.8085</v>
+        <v>407.126053999998</v>
       </c>
       <c r="C33" t="n">
-        <v>13.1147</v>
+        <v>386.6702437189973</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="5" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
-        <v>13.0803</v>
+        <v>398.5112036021808</v>
       </c>
       <c r="C34" t="n">
-        <v>12.432</v>
+        <v>378.7597595760274</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="5" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
-        <v>12.1383</v>
+        <v>357.8823319888601</v>
       </c>
       <c r="C35" t="n">
-        <v>11.655</v>
+        <v>343.632846389541</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="5" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
-        <v>10.7551</v>
+        <v>327.6704544897146</v>
       </c>
       <c r="C36" t="n">
-        <v>10.4041</v>
+        <v>316.9767064514919</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="A37" s="5" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
-        <v>12.3464</v>
+        <v>364.0178957240522</v>
       </c>
       <c r="C37" t="n">
-        <v>11.7556</v>
+        <v>346.5989093965583</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
+      <c r="A38" s="5" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
-        <v>12.3654</v>
+        <v>364.5780865504273</v>
       </c>
       <c r="C38" t="n">
-        <v>11.7377</v>
+        <v>346.0711506706577</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="A39" s="5" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
-        <v>10.9818</v>
+        <v>346.114359581948</v>
       </c>
       <c r="C39" t="n">
-        <v>10.3958</v>
+        <v>327.6453458760872</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="A40" s="5" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
-        <v>10.5614</v>
+        <v>311.389441772501</v>
       </c>
       <c r="C40" t="n">
-        <v>9.9346</v>
+        <v>292.9090412476649</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
+      <c r="A41" s="5" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
-        <v>10.501</v>
+        <v>319.9289121064884</v>
       </c>
       <c r="C41" t="n">
-        <v>9.944800000000001</v>
+        <v>302.9834344459201</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
+      <c r="A42" s="5" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
-        <v>11.4424</v>
+        <v>337.3646058796811</v>
       </c>
       <c r="C42" t="n">
-        <v>10.7858</v>
+        <v>318.0055902692674</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
+      <c r="A43" s="5" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
-        <v>10.9715</v>
+        <v>334.2634091206873</v>
       </c>
       <c r="C43" t="n">
-        <v>10.3133</v>
+        <v>314.2103465601225</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
+      <c r="A44" s="5" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
-        <v>11.125</v>
+        <v>328.0064707064473</v>
       </c>
       <c r="C44" t="n">
-        <v>10.4457</v>
+        <v>307.9781744771539</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="n">
+      <c r="A45" s="5" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
-        <v>11.0581</v>
+        <v>326.0340093230531</v>
       </c>
       <c r="C45" t="n">
-        <v>10.4032</v>
+        <v>306.725116049736</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n">
+      <c r="A46" s="5" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
-        <v>9.979100000000001</v>
+        <v>304.0284360348404</v>
       </c>
       <c r="C46" t="n">
-        <v>9.376200000000001</v>
+        <v>285.6601719543717</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="n">
+      <c r="A47" s="5" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
-        <v>9.735099999999999</v>
+        <v>287.0270375707267</v>
       </c>
       <c r="C47" t="n">
-        <v>9.127700000000001</v>
+        <v>269.1186213633474</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="n">
+      <c r="A48" s="5" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
-        <v>9.699</v>
+        <v>295.4947641673014</v>
       </c>
       <c r="C48" t="n">
-        <v>9.139200000000001</v>
+        <v>278.4396070396742</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n">
+      <c r="A49" s="5" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
-        <v>8.4693</v>
+        <v>249.7065350430665</v>
       </c>
       <c r="C49" t="n">
-        <v>8.031499999999999</v>
+        <v>236.798559054277</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="n">
+      <c r="A50" s="5" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
-        <v>9.2867</v>
+        <v>273.8065340682754</v>
       </c>
       <c r="C50" t="n">
-        <v>8.691000000000001</v>
+        <v>256.2430774750322</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="n">
+      <c r="A51" s="5" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
-        <v>8.7531</v>
+        <v>285.7248044974598</v>
       </c>
       <c r="C51" t="n">
-        <v>8.207100000000001</v>
+        <v>267.9018911004218</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="n">
+      <c r="A52" s="5" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
-        <v>9.6335</v>
+        <v>284.0314908360054</v>
       </c>
       <c r="C52" t="n">
-        <v>9.030900000000001</v>
+        <v>266.264596521605</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="n">
+      <c r="A53" s="5" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
-        <v>9.3973</v>
+        <v>286.3030154974101</v>
       </c>
       <c r="C53" t="n">
-        <v>8.871600000000001</v>
+        <v>270.2867666549779</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="n">
+      <c r="A54" s="5" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
-        <v>9.2287</v>
+        <v>272.0964778614464</v>
       </c>
       <c r="C54" t="n">
-        <v>8.6972</v>
+        <v>256.4258765867967</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="n">
+      <c r="A55" s="5" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
-        <v>8.7156</v>
+        <v>265.5339897491011</v>
       </c>
       <c r="C55" t="n">
-        <v>8.1599</v>
+        <v>248.6037453478464</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="n">
+      <c r="A56" s="5" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
-        <v>9.2098</v>
+        <v>271.5392354078417</v>
       </c>
       <c r="C56" t="n">
-        <v>8.6934</v>
+        <v>256.3138384215217</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="n">
+      <c r="A57" s="5" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
-        <v>8.9581</v>
+        <v>264.1181811447574</v>
       </c>
       <c r="C57" t="n">
-        <v>8.411099999999999</v>
+        <v>247.9905820906965</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="n">
+      <c r="A58" s="5" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
-        <v>8.9085</v>
+        <v>271.4109811923295</v>
       </c>
       <c r="C58" t="n">
-        <v>8.3935</v>
+        <v>255.7207240992106</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="n">
+      <c r="A59" s="5" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
-        <v>9.1434</v>
+        <v>269.5815158882994</v>
       </c>
       <c r="C59" t="n">
-        <v>8.6294</v>
+        <v>254.4268798484689</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="n">
+      <c r="A60" s="5" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
-        <v>8.895799999999999</v>
+        <v>271.0240564057613</v>
       </c>
       <c r="C60" t="n">
-        <v>8.4154</v>
+        <v>256.387940857151</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="n">
+      <c r="A61" s="5" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
-        <v>8.7301</v>
+        <v>257.3958912282567</v>
       </c>
       <c r="C61" t="n">
-        <v>8.2403</v>
+        <v>242.9547613988618</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="n">
+      <c r="A62" s="5" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
-        <v>7.8377</v>
+        <v>231.0846126252515</v>
       </c>
       <c r="C62" t="n">
-        <v>7.4684</v>
+        <v>220.1962719841826</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="n">
+      <c r="A63" s="5" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
-        <v>6.9152</v>
+        <v>225.7307888703241</v>
       </c>
       <c r="C63" t="n">
-        <v>6.6043</v>
+        <v>215.5821738975419</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="n">
+      <c r="A64" s="5" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">
-        <v>8.2067</v>
+        <v>241.9641081480091</v>
       </c>
       <c r="C64" t="n">
-        <v>7.7479</v>
+        <v>228.4369738774367</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="n">
+      <c r="A65" s="5" t="n">
         <v>46113</v>
       </c>
       <c r="B65" t="n">
-        <v>7.7359</v>
+        <v>235.6859414498223</v>
       </c>
       <c r="C65" t="n">
-        <v>7.3651</v>
+        <v>224.3889563427767</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="n">
+      <c r="A66" s="5" t="n">
         <v>46143</v>
       </c>
       <c r="B66" t="n">
-        <v>7.2347</v>
+        <v>213.3059248197694</v>
       </c>
       <c r="C66" t="n">
-        <v>6.8817</v>
+        <v>202.898168940275</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="n">
+      <c r="A67" s="5" t="n">
         <v>46174</v>
       </c>
       <c r="B67" t="n">
-        <v>6.8375</v>
+        <v>208.3148211149523</v>
       </c>
       <c r="C67" t="n">
-        <v>6.4595</v>
+        <v>196.7984770737893</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="n">
+      <c r="A68" s="5" t="n">
         <v>46204</v>
       </c>
       <c r="B68" t="n">
-        <v>7.4131</v>
+        <v>218.5658218421542</v>
       </c>
       <c r="C68" t="n">
-        <v>7.0291</v>
+        <v>207.2440704038372</v>
       </c>
     </row>
   </sheetData>
@@ -1943,539 +1942,539 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
-        <v>0.6778999999999999</v>
+        <v>19.98701901050792</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0404</v>
+        <v>1.318765020586692</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
-        <v>0.3833</v>
+        <v>11.30111282892416</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
-        <v>0.5083</v>
+        <v>15.48613141831521</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="5" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.4385</v>
+        <v>-12.92861459818222</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="5" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.1452</v>
+        <v>-4.423738504700706</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="5" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
-        <v>0.0828</v>
+        <v>2.441252653887087</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="5" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3495</v>
+        <v>10.30456283253064</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="5" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.1683</v>
+        <v>-5.127515084994001</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="5" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
-        <v>1.0035</v>
+        <v>29.58692075091415</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="5" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8157</v>
+        <v>24.85153924438269</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="5" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
-        <v>0.9798</v>
+        <v>28.88815640433052</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="5" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
-        <v>0.1193</v>
+        <v>3.517408715081273</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="5" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
-        <v>0.2322</v>
+        <v>7.579634598520543</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="5" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
-        <v>-0.7299</v>
+        <v>-21.52017285111334</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="5" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
-        <v>-0.6182</v>
+        <v>-18.83440181546815</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="5" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
-        <v>-1.1986</v>
+        <v>-35.33919602595486</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="5" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
-        <v>-0.6052</v>
+        <v>-18.43833707331176</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="5" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
-        <v>0.7879</v>
+        <v>23.23022905794246</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="5" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
-        <v>1.588</v>
+        <v>46.82015959387311</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="5" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
-        <v>0.5941</v>
+        <v>18.10015871654745</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="5" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
-        <v>-0.4112</v>
+        <v>-12.12370883186437</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="5" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
-        <v>0.2474</v>
+        <v>7.537416708422554</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="5" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
-        <v>-3.7416</v>
+        <v>-110.3163155771005</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="5" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
-        <v>-0.1221</v>
+        <v>-3.599963152652334</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="5" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
-        <v>0.156</v>
+        <v>5.092260970582276</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="5" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
-        <v>-0.1164</v>
+        <v>-3.431905904739818</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="5" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
-        <v>0.8033</v>
+        <v>24.47375441340274</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="5" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
-        <v>0.2889</v>
+        <v>8.517848933671248</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="5" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
-        <v>0.101</v>
+        <v>3.077118381368948</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="5" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
-        <v>-0.0805</v>
+        <v>-2.373440080168001</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="5" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
-        <v>-0.6892</v>
+        <v>-20.32018513356256</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="5" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
-        <v>-0.2742</v>
+        <v>-8.353919407637283</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="5" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
-        <v>-0.3769</v>
+        <v>-11.11241697161888</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="5" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
-        <v>-0.4145</v>
+        <v>-12.62837197106365</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="A37" s="5" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
-        <v>-0.172</v>
+        <v>-5.071201165079455</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
+      <c r="A38" s="5" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
-        <v>-0.0193</v>
+        <v>-0.5690359446862412</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="A39" s="5" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
-        <v>0.2722</v>
+        <v>8.57895141763702</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="A40" s="5" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
-        <v>-1.0239</v>
+        <v>-30.18838879607473</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
+      <c r="A41" s="5" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
-        <v>0.0524</v>
+        <v>1.596445576076564</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
+      <c r="A42" s="5" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
-        <v>-0.3796</v>
+        <v>-11.19202303641954</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
+      <c r="A43" s="5" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
-        <v>-0.2887</v>
+        <v>-8.795683927734807</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
+      <c r="A44" s="5" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
-        <v>-0.8908</v>
+        <v>-26.26410463867895</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="n">
+      <c r="A45" s="5" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
-        <v>-0.0146</v>
+        <v>-0.4304624244776747</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n">
+      <c r="A46" s="5" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
-        <v>1.6989</v>
+        <v>51.75956849611591</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="n">
+      <c r="A47" s="5" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
-        <v>1.4887</v>
+        <v>43.89242543287084</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="n">
+      <c r="A48" s="5" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
-        <v>0.6367</v>
+        <v>19.39803241007534</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n">
+      <c r="A49" s="5" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
-        <v>0.2114</v>
+        <v>6.232860036615098</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="n">
+      <c r="A50" s="5" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
-        <v>-0.4569</v>
+        <v>-13.4711151879349</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="n">
+      <c r="A51" s="5" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
-        <v>-1.0654</v>
+        <v>-34.7775310131946</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="n">
+      <c r="A52" s="5" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
-        <v>-0.9341</v>
+        <v>-27.54075004825999</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="n">
+      <c r="A53" s="5" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
-        <v>-0.2647</v>
+        <v>-8.064487480676839</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="n">
+      <c r="A54" s="5" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
-        <v>0.348</v>
+        <v>10.26033724097471</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="n">
+      <c r="A55" s="5" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
-        <v>0.8498</v>
+        <v>25.89044752957755</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="n">
+      <c r="A56" s="5" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
-        <v>-0.1341</v>
+        <v>-3.953767885099738</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="n">
+      <c r="A57" s="5" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
-        <v>-1.6852</v>
+        <v>-49.68597792669708</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="n">
+      <c r="A58" s="5" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
-        <v>-0.5364</v>
+        <v>-16.34224059174558</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="n">
+      <c r="A59" s="5" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
-        <v>0.8952</v>
+        <v>26.39383304057633</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="n">
+      <c r="A60" s="5" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
-        <v>1.2117</v>
+        <v>36.91628062083916</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="n">
+      <c r="A61" s="5" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
-        <v>1.1908</v>
+        <v>35.10922294986405</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="n">
+      <c r="A62" s="5" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
-        <v>0.3538</v>
+        <v>10.43134286165762</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="n">
+      <c r="A63" s="5" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
-        <v>0.2049</v>
+        <v>6.688488928668646</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="n">
+      <c r="A64" s="5" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">
-        <v>0.0122</v>
+        <v>0.359701477988194</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="n">
+      <c r="A65" s="5" t="n">
         <v>46113</v>
       </c>
       <c r="B65" t="n">
-        <v>-0.5137</v>
+        <v>-15.65065061890326</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="n">
+      <c r="A66" s="5" t="n">
         <v>46143</v>
       </c>
       <c r="B66" t="n">
-        <v>0.3952</v>
+        <v>11.65196918860117</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="n">
+      <c r="A67" s="5" t="n">
         <v>46174</v>
       </c>
       <c r="B67" t="n">
-        <v>0.3971</v>
+        <v>12.09825454694663</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="n">
+      <c r="A68" s="5" t="n">
         <v>46204</v>
       </c>
       <c r="B68" t="n">
-        <v>-0.8085</v>
+        <v>-23.83759384864383</v>
       </c>
     </row>
   </sheetData>
@@ -2529,440 +2528,440 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>44286</v>
       </c>
       <c r="B2" t="n">
-        <v>10.0325</v>
+        <v>101.8851160431815</v>
       </c>
       <c r="C2" t="n">
-        <v>10.37</v>
+        <v>105.3125993887657</v>
       </c>
       <c r="D2" t="n">
-        <v>14.1018</v>
+        <v>143.2109174600285</v>
       </c>
       <c r="E2" t="n">
-        <v>2.4602</v>
+        <v>24.9845763757224</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>44377</v>
       </c>
       <c r="B3" t="n">
-        <v>11.9176</v>
+        <v>119.6992689211269</v>
       </c>
       <c r="C3" t="n">
-        <v>8.854900000000001</v>
+        <v>88.93779421776925</v>
       </c>
       <c r="D3" t="n">
-        <v>12.7834</v>
+        <v>128.3952838093521</v>
       </c>
       <c r="E3" t="n">
-        <v>3.8068</v>
+        <v>38.23514608049825</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>44469</v>
       </c>
       <c r="B4" t="n">
-        <v>12.7202</v>
+        <v>126.3718076884071</v>
       </c>
       <c r="C4" t="n">
-        <v>7.5897</v>
+        <v>75.40165318255244</v>
       </c>
       <c r="D4" t="n">
-        <v>12.998</v>
+        <v>129.1316768866776</v>
       </c>
       <c r="E4" t="n">
-        <v>5.357</v>
+        <v>53.22037183273824</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>44561</v>
       </c>
       <c r="B5" t="n">
-        <v>8.254100000000001</v>
+        <v>82.0022906747442</v>
       </c>
       <c r="C5" t="n">
-        <v>11.0135</v>
+        <v>109.416196598817</v>
       </c>
       <c r="D5" t="n">
-        <v>15.2887</v>
+        <v>151.8891728279233</v>
       </c>
       <c r="E5" t="n">
-        <v>3.2322</v>
+        <v>32.11104831767342</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="5" t="n">
         <v>44651</v>
       </c>
       <c r="B6" t="n">
-        <v>12.2542</v>
+        <v>124.4476041880243</v>
       </c>
       <c r="C6" t="n">
-        <v>10.7558</v>
+        <v>109.2305936842513</v>
       </c>
       <c r="D6" t="n">
-        <v>14.3389</v>
+        <v>145.6187879822153</v>
       </c>
       <c r="E6" t="n">
-        <v>2.2486</v>
+        <v>22.83567126186871</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="5" t="n">
         <v>44742</v>
       </c>
       <c r="B7" t="n">
-        <v>13.9404</v>
+        <v>140.016084485809</v>
       </c>
       <c r="C7" t="n">
-        <v>7.2054</v>
+        <v>72.37036922570717</v>
       </c>
       <c r="D7" t="n">
-        <v>12.0683</v>
+        <v>121.2128857421659</v>
       </c>
       <c r="E7" t="n">
-        <v>3.5362</v>
+        <v>35.5172647814064</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="5" t="n">
         <v>44834</v>
       </c>
       <c r="B8" t="n">
-        <v>10.4248</v>
+        <v>103.5676184957867</v>
       </c>
       <c r="C8" t="n">
-        <v>6.2656</v>
+        <v>62.24707144954353</v>
       </c>
       <c r="D8" t="n">
-        <v>11.5841</v>
+        <v>115.0849560103833</v>
       </c>
       <c r="E8" t="n">
-        <v>5.0118</v>
+        <v>49.79090154028702</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="5" t="n">
         <v>44926</v>
       </c>
       <c r="B9" t="n">
-        <v>5.3704</v>
+        <v>53.3534972728276</v>
       </c>
       <c r="C9" t="n">
-        <v>11.0372</v>
+        <v>109.6516498025571</v>
       </c>
       <c r="D9" t="n">
-        <v>12.8562</v>
+        <v>127.7229315579708</v>
       </c>
       <c r="E9" t="n">
-        <v>3.4408</v>
+        <v>34.18343389996001</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="5" t="n">
         <v>45016</v>
       </c>
       <c r="B10" t="n">
-        <v>10.959</v>
+        <v>111.2941925459482</v>
       </c>
       <c r="C10" t="n">
-        <v>11.1361</v>
+        <v>113.0927326955866</v>
       </c>
       <c r="D10" t="n">
-        <v>13.8375</v>
+        <v>140.5268171689532</v>
       </c>
       <c r="E10" t="n">
-        <v>2.4807</v>
+        <v>25.19276425300974</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="5" t="n">
         <v>45107</v>
       </c>
       <c r="B11" t="n">
-        <v>8.7355</v>
+        <v>87.73855169333626</v>
       </c>
       <c r="C11" t="n">
-        <v>11.1039</v>
+        <v>111.5265416000958</v>
       </c>
       <c r="D11" t="n">
-        <v>13.2965</v>
+        <v>133.5488126140971</v>
       </c>
       <c r="E11" t="n">
-        <v>3.7295</v>
+        <v>37.45875205086114</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="5" t="n">
         <v>45199</v>
       </c>
       <c r="B12" t="n">
-        <v>15.6772</v>
+        <v>155.7488171170812</v>
       </c>
       <c r="C12" t="n">
-        <v>6.6875</v>
+        <v>66.43853586549132</v>
       </c>
       <c r="D12" t="n">
-        <v>11.6934</v>
+        <v>116.1708224732017</v>
       </c>
       <c r="E12" t="n">
-        <v>5.2584</v>
+        <v>52.2408070273046</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="5" t="n">
         <v>45291</v>
       </c>
       <c r="B13" t="n">
-        <v>7.6076</v>
+        <v>75.57948492714941</v>
       </c>
       <c r="C13" t="n">
-        <v>9.696099999999999</v>
+        <v>96.32817758585276</v>
       </c>
       <c r="D13" t="n">
-        <v>14.9384</v>
+        <v>148.4090353903634</v>
       </c>
       <c r="E13" t="n">
-        <v>3.46</v>
+        <v>34.37418079919252</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="5" t="n">
         <v>45382</v>
       </c>
       <c r="B14" t="n">
-        <v>10.9467</v>
+        <v>109.947639381998</v>
       </c>
       <c r="C14" t="n">
-        <v>7.472</v>
+        <v>75.04807489583979</v>
       </c>
       <c r="D14" t="n">
-        <v>12.1158</v>
+        <v>121.6899713360567</v>
       </c>
       <c r="E14" t="n">
-        <v>2.5735</v>
+        <v>25.84799528164397</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="5" t="n">
         <v>45473</v>
       </c>
       <c r="B15" t="n">
-        <v>11.091</v>
+        <v>111.3969751967022</v>
       </c>
       <c r="C15" t="n">
-        <v>5.5315</v>
+        <v>55.55787289699381</v>
       </c>
       <c r="D15" t="n">
-        <v>10.7047</v>
+        <v>107.5170138299647</v>
       </c>
       <c r="E15" t="n">
-        <v>4.0446</v>
+        <v>40.62358722212441</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="5" t="n">
         <v>45565</v>
       </c>
       <c r="B16" t="n">
-        <v>11.4142</v>
+        <v>113.3970446468622</v>
       </c>
       <c r="C16" t="n">
-        <v>2.8507</v>
+        <v>28.32094716886072</v>
       </c>
       <c r="D16" t="n">
-        <v>9.438199999999998</v>
+        <v>93.76600960084934</v>
       </c>
       <c r="E16" t="n">
-        <v>5.0576</v>
+        <v>50.24591237283123</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="5" t="n">
         <v>45657</v>
       </c>
       <c r="B17" t="n">
-        <v>5.2247</v>
+        <v>51.90600648021422</v>
       </c>
       <c r="C17" t="n">
-        <v>4.6377</v>
+        <v>46.0743174255535</v>
       </c>
       <c r="D17" t="n">
-        <v>11.1899</v>
+        <v>111.1686837355157</v>
       </c>
       <c r="E17" t="n">
-        <v>3.3572</v>
+        <v>33.35289010955177</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="5" t="n">
         <v>45747</v>
       </c>
       <c r="B18" t="n">
-        <v>11.1018</v>
+        <v>112.7443988326132</v>
       </c>
       <c r="C18" t="n">
-        <v>5.0315</v>
+        <v>51.09742949128009</v>
       </c>
       <c r="D18" t="n">
-        <v>10.4643</v>
+        <v>106.2702636242874</v>
       </c>
       <c r="E18" t="n">
-        <v>2.4617</v>
+        <v>24.99980963503611</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="5" t="n">
         <v>45838</v>
       </c>
       <c r="B19" t="n">
-        <v>10.8502</v>
+        <v>108.9784023333567</v>
       </c>
       <c r="C19" t="n">
-        <v>2.3419</v>
+        <v>23.52182636490461</v>
       </c>
       <c r="D19" t="n">
-        <v>8.555000000000001</v>
+        <v>85.92562643655107</v>
       </c>
       <c r="E19" t="n">
-        <v>3.3139</v>
+        <v>33.28450420199726</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="5" t="n">
         <v>45930</v>
       </c>
       <c r="B20" t="n">
-        <v>8.978999999999999</v>
+        <v>89.20397959420508</v>
       </c>
       <c r="C20" t="n">
-        <v>4.1775</v>
+        <v>41.50235268457421</v>
       </c>
       <c r="D20" t="n">
-        <v>10.3794</v>
+        <v>103.1165815569765</v>
       </c>
       <c r="E20" t="n">
-        <v>4.8892</v>
+        <v>48.57290311081273</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="5" t="n">
         <v>46022</v>
       </c>
       <c r="B21" t="n">
-        <v>3.157</v>
+        <v>31.36395629567942</v>
       </c>
       <c r="C21" t="n">
-        <v>5.3483</v>
+        <v>53.13393964402351</v>
       </c>
       <c r="D21" t="n">
-        <v>11.3777</v>
+        <v>113.0344268436337</v>
       </c>
       <c r="E21" t="n">
-        <v>2.8225</v>
+        <v>28.04078766061297</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="5" t="n">
         <v>46112</v>
       </c>
       <c r="B22" t="n">
-        <v>4.682399999999999</v>
+        <v>47.55214227366985</v>
       </c>
       <c r="C22" t="n">
-        <v>4.7073</v>
+        <v>47.8050143782774</v>
       </c>
       <c r="D22" t="n">
-        <v>10.4308</v>
+        <v>105.9300541662813</v>
       </c>
       <c r="E22" t="n">
-        <v>2.0675</v>
+        <v>20.99650908739373</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="5" t="n">
         <v>46203</v>
       </c>
       <c r="B23" t="n">
-        <v>7.166</v>
+        <v>71.97463928045876</v>
       </c>
       <c r="C23" t="n">
-        <v>2.1376</v>
+        <v>21.46985611581198</v>
       </c>
       <c r="D23" t="n">
-        <v>7.663800000000001</v>
+        <v>76.97449630443482</v>
       </c>
       <c r="E23" t="n">
-        <v>2.9714</v>
+        <v>29.84446597236327</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>

--- a/output/Data and Chart Outputs/nz_gas.xlsx
+++ b/output/Data and Chart Outputs/nz_gas.xlsx
@@ -23,8 +23,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="mmm/yy"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="mmm/yy"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,13 +64,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -159,7 +158,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>New Zealand gas production (MBIE) (to Jul/26)</a:t>
+              <a:t>New Zealand gas production (MBIE) (to Aug/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -195,12 +194,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$68</f>
+              <f>'Chart'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$68</f>
+              <f>'Chart'!$B$2:$B$69</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -231,12 +230,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$68</f>
+              <f>'Chart'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$68</f>
+              <f>'Chart'!$C$2:$C$69</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -335,7 +334,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>New Zealand gas stock change, Ahuroa storage (MBIE) (to Jul/26)</a:t>
+              <a:t>New Zealand gas stock change, Ahuroa storage (MBIE) (to Aug/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -365,12 +364,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart - Storage'!$A$2:$A$68</f>
+              <f>'Chart - Storage'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Storage'!$B$2:$B$68</f>
+              <f>'Chart - Storage'!$B$2:$B$69</f>
             </numRef>
           </val>
         </ser>
@@ -1105,6 +1104,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -1115,10 +1115,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>New Zealand. Monthly Jan 2010 to Jul 2026 (MBIE history from 1974, kept here from 2010).</t>
+          <t>New Zealand. Monthly Jan 2010 to Aug 2026 (MBIE history from 1974, kept here from 2010).</t>
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
@@ -1129,7 +1130,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MBIE (Ministry of Business, Innovation and Employment) energy statistics: https://www.mbie.govt.nz/assets/Data-Files/Energy/monthly-gas-webtable-sept-2026.xlsx; https://www.mbie.govt.nz/assets/Data-Files/Energy/nz-energy-quarterly-and-energy-in-nz/gas-quarterly-webtable-june-2026.xlsx</t>
+          <t>MBIE (Ministry of Business, Innovation and Employment) energy statistics: https://www.mbie.govt.nz/assets/Data-Files/Energy/monthly-gas-webtable-october-2026.xlsx; https://www.mbie.govt.nz/assets/Data-Files/Energy/nz-energy-quarterly-and-energy-in-nz/gas-quarterly-webtable-june-2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C68"/>
+  <dimension ref="A1:C69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1175,7 +1176,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -1186,7 +1187,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="3" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -1197,7 +1198,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="3" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -1208,7 +1209,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="3" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -1219,7 +1220,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="3" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -1230,7 +1231,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="3" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -1241,7 +1242,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="3" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -1252,7 +1253,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="3" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -1263,7 +1264,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="3" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -1274,7 +1275,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="3" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -1285,7 +1286,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="3" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -1296,7 +1297,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="3" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -1307,7 +1308,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="3" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -1318,7 +1319,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="3" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -1329,7 +1330,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="3" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -1340,7 +1341,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="3" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -1351,7 +1352,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="3" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -1362,7 +1363,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="3" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -1373,7 +1374,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="3" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -1384,7 +1385,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="3" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -1395,7 +1396,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="3" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -1406,7 +1407,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="3" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -1417,7 +1418,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="3" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -1428,7 +1429,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="3" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -1439,7 +1440,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="3" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -1450,7 +1451,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="3" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -1461,7 +1462,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="n">
+      <c r="A28" s="3" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -1472,7 +1473,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n">
+      <c r="A29" s="3" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -1483,7 +1484,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="n">
+      <c r="A30" s="3" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -1494,7 +1495,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="n">
+      <c r="A31" s="3" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -1505,7 +1506,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="n">
+      <c r="A32" s="3" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -1516,7 +1517,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="n">
+      <c r="A33" s="3" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -1527,7 +1528,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="n">
+      <c r="A34" s="3" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -1538,7 +1539,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="n">
+      <c r="A35" s="3" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -1549,7 +1550,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="n">
+      <c r="A36" s="3" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -1560,7 +1561,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="n">
+      <c r="A37" s="3" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -1571,7 +1572,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="n">
+      <c r="A38" s="3" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -1582,7 +1583,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="n">
+      <c r="A39" s="3" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -1593,7 +1594,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="n">
+      <c r="A40" s="3" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -1604,7 +1605,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="n">
+      <c r="A41" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -1615,7 +1616,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="n">
+      <c r="A42" s="3" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -1626,7 +1627,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="n">
+      <c r="A43" s="3" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -1637,7 +1638,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="n">
+      <c r="A44" s="3" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -1648,7 +1649,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="n">
+      <c r="A45" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -1659,7 +1660,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="n">
+      <c r="A46" s="3" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -1670,7 +1671,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="n">
+      <c r="A47" s="3" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -1681,7 +1682,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="n">
+      <c r="A48" s="3" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -1692,7 +1693,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="n">
+      <c r="A49" s="3" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -1703,7 +1704,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="n">
+      <c r="A50" s="3" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -1714,7 +1715,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="n">
+      <c r="A51" s="3" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -1725,7 +1726,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="n">
+      <c r="A52" s="3" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -1736,7 +1737,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="n">
+      <c r="A53" s="3" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -1747,7 +1748,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="n">
+      <c r="A54" s="3" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -1758,7 +1759,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="n">
+      <c r="A55" s="3" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -1769,7 +1770,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="n">
+      <c r="A56" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -1780,7 +1781,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="n">
+      <c r="A57" s="3" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -1791,7 +1792,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="5" t="n">
+      <c r="A58" s="3" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -1802,7 +1803,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="5" t="n">
+      <c r="A59" s="3" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -1813,7 +1814,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="5" t="n">
+      <c r="A60" s="3" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -1824,7 +1825,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="n">
+      <c r="A61" s="3" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
@@ -1835,7 +1836,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="5" t="n">
+      <c r="A62" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -1846,7 +1847,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="5" t="n">
+      <c r="A63" s="3" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
@@ -1857,7 +1858,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="5" t="n">
+      <c r="A64" s="3" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">
@@ -1868,7 +1869,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="5" t="n">
+      <c r="A65" s="3" t="n">
         <v>46113</v>
       </c>
       <c r="B65" t="n">
@@ -1879,7 +1880,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="5" t="n">
+      <c r="A66" s="3" t="n">
         <v>46143</v>
       </c>
       <c r="B66" t="n">
@@ -1890,7 +1891,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="5" t="n">
+      <c r="A67" s="3" t="n">
         <v>46174</v>
       </c>
       <c r="B67" t="n">
@@ -1901,7 +1902,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="5" t="n">
+      <c r="A68" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="B68" t="n">
@@ -1909,6 +1910,17 @@
       </c>
       <c r="C68" t="n">
         <v>207.2440704038372</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B69" t="n">
+        <v>220.3171552677688</v>
+      </c>
+      <c r="C69" t="n">
+        <v>209.1103903674973</v>
       </c>
     </row>
   </sheetData>
@@ -1923,7 +1935,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B68"/>
+  <dimension ref="A1:B69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1942,7 +1954,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -1950,7 +1962,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="3" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -1958,7 +1970,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="3" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -1966,7 +1978,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="3" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -1974,7 +1986,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="3" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -1982,7 +1994,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="3" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -1990,7 +2002,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="3" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -1998,7 +2010,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="3" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -2006,7 +2018,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="3" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -2014,7 +2026,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="3" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -2022,7 +2034,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="3" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -2030,7 +2042,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="3" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -2038,7 +2050,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="3" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -2046,7 +2058,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="3" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -2054,7 +2066,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="3" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -2062,7 +2074,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="3" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -2070,7 +2082,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="3" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -2078,7 +2090,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="3" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -2086,7 +2098,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="3" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -2094,7 +2106,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="3" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -2102,7 +2114,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="3" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -2110,7 +2122,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="3" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -2118,7 +2130,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="3" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -2126,7 +2138,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="3" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -2134,7 +2146,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="3" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -2142,7 +2154,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="3" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -2150,7 +2162,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="n">
+      <c r="A28" s="3" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -2158,7 +2170,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n">
+      <c r="A29" s="3" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -2166,7 +2178,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="n">
+      <c r="A30" s="3" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -2174,7 +2186,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="n">
+      <c r="A31" s="3" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -2182,7 +2194,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="n">
+      <c r="A32" s="3" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -2190,7 +2202,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="n">
+      <c r="A33" s="3" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -2198,7 +2210,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="n">
+      <c r="A34" s="3" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -2206,7 +2218,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="n">
+      <c r="A35" s="3" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -2214,7 +2226,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="n">
+      <c r="A36" s="3" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -2222,7 +2234,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="n">
+      <c r="A37" s="3" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -2230,7 +2242,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="n">
+      <c r="A38" s="3" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -2238,7 +2250,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="n">
+      <c r="A39" s="3" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -2246,7 +2258,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="n">
+      <c r="A40" s="3" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -2254,7 +2266,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="n">
+      <c r="A41" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -2262,7 +2274,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="n">
+      <c r="A42" s="3" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -2270,7 +2282,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="n">
+      <c r="A43" s="3" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -2278,7 +2290,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="n">
+      <c r="A44" s="3" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -2286,7 +2298,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="n">
+      <c r="A45" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -2294,7 +2306,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="n">
+      <c r="A46" s="3" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -2302,7 +2314,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="n">
+      <c r="A47" s="3" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -2310,7 +2322,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="n">
+      <c r="A48" s="3" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -2318,7 +2330,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="n">
+      <c r="A49" s="3" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -2326,7 +2338,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="n">
+      <c r="A50" s="3" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -2334,7 +2346,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="n">
+      <c r="A51" s="3" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -2342,7 +2354,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="n">
+      <c r="A52" s="3" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -2350,7 +2362,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="n">
+      <c r="A53" s="3" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -2358,7 +2370,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="n">
+      <c r="A54" s="3" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -2366,7 +2378,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="n">
+      <c r="A55" s="3" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -2374,7 +2386,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="n">
+      <c r="A56" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -2382,7 +2394,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="n">
+      <c r="A57" s="3" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -2390,7 +2402,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="5" t="n">
+      <c r="A58" s="3" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -2398,7 +2410,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="5" t="n">
+      <c r="A59" s="3" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -2406,7 +2418,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="5" t="n">
+      <c r="A60" s="3" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -2414,7 +2426,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="n">
+      <c r="A61" s="3" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
@@ -2422,7 +2434,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="5" t="n">
+      <c r="A62" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -2430,7 +2442,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="5" t="n">
+      <c r="A63" s="3" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
@@ -2438,7 +2450,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="5" t="n">
+      <c r="A64" s="3" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">
@@ -2446,7 +2458,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="5" t="n">
+      <c r="A65" s="3" t="n">
         <v>46113</v>
       </c>
       <c r="B65" t="n">
@@ -2454,7 +2466,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="5" t="n">
+      <c r="A66" s="3" t="n">
         <v>46143</v>
       </c>
       <c r="B66" t="n">
@@ -2462,7 +2474,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="5" t="n">
+      <c r="A67" s="3" t="n">
         <v>46174</v>
       </c>
       <c r="B67" t="n">
@@ -2470,11 +2482,19 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="5" t="n">
+      <c r="A68" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="B68" t="n">
         <v>-23.83759384864383</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B69" t="n">
+        <v>-30.11173110404447</v>
       </c>
     </row>
   </sheetData>
@@ -2528,7 +2548,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
         <v>44286</v>
       </c>
       <c r="B2" t="n">
@@ -2548,7 +2568,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="3" t="n">
         <v>44377</v>
       </c>
       <c r="B3" t="n">
@@ -2568,7 +2588,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="3" t="n">
         <v>44469</v>
       </c>
       <c r="B4" t="n">
@@ -2588,7 +2608,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="3" t="n">
         <v>44561</v>
       </c>
       <c r="B5" t="n">
@@ -2608,7 +2628,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="3" t="n">
         <v>44651</v>
       </c>
       <c r="B6" t="n">
@@ -2628,7 +2648,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="3" t="n">
         <v>44742</v>
       </c>
       <c r="B7" t="n">
@@ -2648,7 +2668,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="3" t="n">
         <v>44834</v>
       </c>
       <c r="B8" t="n">
@@ -2668,7 +2688,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="3" t="n">
         <v>44926</v>
       </c>
       <c r="B9" t="n">
@@ -2688,7 +2708,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="3" t="n">
         <v>45016</v>
       </c>
       <c r="B10" t="n">
@@ -2708,7 +2728,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="3" t="n">
         <v>45107</v>
       </c>
       <c r="B11" t="n">
@@ -2728,7 +2748,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="3" t="n">
         <v>45199</v>
       </c>
       <c r="B12" t="n">
@@ -2748,7 +2768,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="3" t="n">
         <v>45291</v>
       </c>
       <c r="B13" t="n">
@@ -2768,7 +2788,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="3" t="n">
         <v>45382</v>
       </c>
       <c r="B14" t="n">
@@ -2788,7 +2808,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="3" t="n">
         <v>45473</v>
       </c>
       <c r="B15" t="n">
@@ -2808,7 +2828,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="3" t="n">
         <v>45565</v>
       </c>
       <c r="B16" t="n">
@@ -2828,7 +2848,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="3" t="n">
         <v>45657</v>
       </c>
       <c r="B17" t="n">
@@ -2848,7 +2868,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="3" t="n">
         <v>45747</v>
       </c>
       <c r="B18" t="n">
@@ -2868,7 +2888,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="3" t="n">
         <v>45838</v>
       </c>
       <c r="B19" t="n">
@@ -2888,7 +2908,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="3" t="n">
         <v>45930</v>
       </c>
       <c r="B20" t="n">
@@ -2908,7 +2928,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="3" t="n">
         <v>46022</v>
       </c>
       <c r="B21" t="n">
@@ -2928,7 +2948,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="3" t="n">
         <v>46112</v>
       </c>
       <c r="B22" t="n">
@@ -2948,7 +2968,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="3" t="n">
         <v>46203</v>
       </c>
       <c r="B23" t="n">
@@ -2979,7 +2999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J200"/>
+  <dimension ref="A1:J201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9400,6 +9420,38 @@
       </c>
       <c r="J200" t="n">
         <v>0.0494</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="4" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B201" t="n">
+        <v>7.4725</v>
+      </c>
+      <c r="C201" t="n">
+        <v>0.008800000000000001</v>
+      </c>
+      <c r="D201" t="n">
+        <v>0.3393</v>
+      </c>
+      <c r="E201" t="n">
+        <v>0.0319</v>
+      </c>
+      <c r="F201" t="n">
+        <v>7.0924</v>
+      </c>
+      <c r="G201" t="n">
+        <v>0</v>
+      </c>
+      <c r="H201" t="n">
+        <v>-1.0213</v>
+      </c>
+      <c r="I201" t="n">
+        <v>0.2966</v>
+      </c>
+      <c r="J201" t="n">
+        <v>0.0436</v>
       </c>
     </row>
   </sheetData>

--- a/output/Data and Chart Outputs/nz_gas.xlsx
+++ b/output/Data and Chart Outputs/nz_gas.xlsx
@@ -23,8 +23,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="mmm/yy"/>
+    <numFmt numFmtId="165" formatCode="mmm/yy"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,12 +64,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -158,6 +159,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>New Zealand gas production (MBIE) (to Aug/26)</a:t>
             </a:r>
           </a:p>
@@ -334,6 +336,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>New Zealand gas stock change, Ahuroa storage (MBIE) (to Aug/26)</a:t>
             </a:r>
           </a:p>
@@ -465,6 +468,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>New Zealand gas consumption by sector (MBIE, quarterly) (to Jun/26)</a:t>
             </a:r>
           </a:p>
@@ -1104,7 +1108,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -1119,7 +1122,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
@@ -1176,7 +1178,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -1187,7 +1189,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -1198,7 +1200,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -1209,7 +1211,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -1220,7 +1222,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="5" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -1231,7 +1233,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="5" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -1242,7 +1244,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="5" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -1253,7 +1255,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="5" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -1264,7 +1266,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="5" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -1275,7 +1277,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="5" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -1286,7 +1288,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="5" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -1297,7 +1299,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="5" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -1308,7 +1310,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="5" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -1319,7 +1321,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="5" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -1330,7 +1332,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="5" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -1341,7 +1343,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="5" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -1352,7 +1354,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="5" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -1363,7 +1365,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="5" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -1374,7 +1376,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="5" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -1385,7 +1387,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="5" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -1396,7 +1398,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="5" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -1407,7 +1409,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="5" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -1418,7 +1420,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="5" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -1429,7 +1431,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="5" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -1440,7 +1442,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="5" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -1451,7 +1453,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="5" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -1462,7 +1464,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="5" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -1473,7 +1475,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="5" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -1484,7 +1486,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="5" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -1495,7 +1497,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="5" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -1506,7 +1508,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="5" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -1517,7 +1519,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="5" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -1528,7 +1530,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="5" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -1539,7 +1541,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="5" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -1550,7 +1552,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="5" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -1561,7 +1563,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="A37" s="5" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -1572,7 +1574,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
+      <c r="A38" s="5" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -1583,7 +1585,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="A39" s="5" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -1594,7 +1596,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="A40" s="5" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -1605,7 +1607,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
+      <c r="A41" s="5" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -1616,7 +1618,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
+      <c r="A42" s="5" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -1627,7 +1629,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
+      <c r="A43" s="5" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -1638,7 +1640,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
+      <c r="A44" s="5" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -1649,7 +1651,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="n">
+      <c r="A45" s="5" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -1660,7 +1662,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n">
+      <c r="A46" s="5" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -1671,7 +1673,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="n">
+      <c r="A47" s="5" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -1682,7 +1684,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="n">
+      <c r="A48" s="5" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -1693,7 +1695,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n">
+      <c r="A49" s="5" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -1704,7 +1706,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="n">
+      <c r="A50" s="5" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -1715,7 +1717,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="n">
+      <c r="A51" s="5" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -1726,7 +1728,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="n">
+      <c r="A52" s="5" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -1737,7 +1739,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="n">
+      <c r="A53" s="5" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -1748,7 +1750,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="n">
+      <c r="A54" s="5" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -1759,7 +1761,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="n">
+      <c r="A55" s="5" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -1770,7 +1772,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="n">
+      <c r="A56" s="5" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -1781,7 +1783,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="n">
+      <c r="A57" s="5" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -1792,7 +1794,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="n">
+      <c r="A58" s="5" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -1803,7 +1805,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="n">
+      <c r="A59" s="5" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -1814,7 +1816,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="n">
+      <c r="A60" s="5" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -1825,7 +1827,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="n">
+      <c r="A61" s="5" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
@@ -1836,7 +1838,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="n">
+      <c r="A62" s="5" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -1847,7 +1849,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="n">
+      <c r="A63" s="5" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
@@ -1858,7 +1860,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="n">
+      <c r="A64" s="5" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">
@@ -1869,7 +1871,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="n">
+      <c r="A65" s="5" t="n">
         <v>46113</v>
       </c>
       <c r="B65" t="n">
@@ -1880,7 +1882,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="n">
+      <c r="A66" s="5" t="n">
         <v>46143</v>
       </c>
       <c r="B66" t="n">
@@ -1891,7 +1893,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="n">
+      <c r="A67" s="5" t="n">
         <v>46174</v>
       </c>
       <c r="B67" t="n">
@@ -1902,7 +1904,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="n">
+      <c r="A68" s="5" t="n">
         <v>46204</v>
       </c>
       <c r="B68" t="n">
@@ -1913,7 +1915,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="3" t="n">
+      <c r="A69" s="5" t="n">
         <v>46235</v>
       </c>
       <c r="B69" t="n">
@@ -1954,7 +1956,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -1962,7 +1964,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -1970,7 +1972,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -1978,7 +1980,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -1986,7 +1988,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="5" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -1994,7 +1996,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="5" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -2002,7 +2004,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="5" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -2010,7 +2012,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="5" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -2018,7 +2020,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="5" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -2026,7 +2028,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="5" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -2034,7 +2036,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="5" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -2042,7 +2044,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="5" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -2050,7 +2052,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="5" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -2058,7 +2060,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="5" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -2066,7 +2068,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="5" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -2074,7 +2076,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="5" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -2082,7 +2084,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="5" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -2090,7 +2092,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="5" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -2098,7 +2100,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="5" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -2106,7 +2108,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="5" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -2114,7 +2116,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="5" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -2122,7 +2124,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="5" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -2130,7 +2132,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="5" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -2138,7 +2140,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="5" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -2146,7 +2148,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="5" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -2154,7 +2156,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="5" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -2162,7 +2164,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="5" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -2170,7 +2172,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="5" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -2178,7 +2180,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="5" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -2186,7 +2188,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="5" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -2194,7 +2196,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="5" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -2202,7 +2204,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="5" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -2210,7 +2212,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="5" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -2218,7 +2220,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="5" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -2226,7 +2228,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="5" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -2234,7 +2236,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="A37" s="5" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -2242,7 +2244,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
+      <c r="A38" s="5" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -2250,7 +2252,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="A39" s="5" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -2258,7 +2260,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="A40" s="5" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -2266,7 +2268,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
+      <c r="A41" s="5" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -2274,7 +2276,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
+      <c r="A42" s="5" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -2282,7 +2284,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
+      <c r="A43" s="5" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -2290,7 +2292,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
+      <c r="A44" s="5" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -2298,7 +2300,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="n">
+      <c r="A45" s="5" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -2306,7 +2308,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n">
+      <c r="A46" s="5" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -2314,7 +2316,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="n">
+      <c r="A47" s="5" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -2322,7 +2324,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="n">
+      <c r="A48" s="5" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -2330,7 +2332,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n">
+      <c r="A49" s="5" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -2338,7 +2340,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="n">
+      <c r="A50" s="5" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -2346,7 +2348,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="n">
+      <c r="A51" s="5" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -2354,7 +2356,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="n">
+      <c r="A52" s="5" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -2362,7 +2364,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="n">
+      <c r="A53" s="5" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -2370,7 +2372,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="n">
+      <c r="A54" s="5" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -2378,7 +2380,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="n">
+      <c r="A55" s="5" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -2386,7 +2388,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="n">
+      <c r="A56" s="5" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -2394,7 +2396,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="n">
+      <c r="A57" s="5" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -2402,7 +2404,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="n">
+      <c r="A58" s="5" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -2410,7 +2412,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="n">
+      <c r="A59" s="5" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -2418,7 +2420,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="n">
+      <c r="A60" s="5" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -2426,7 +2428,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="n">
+      <c r="A61" s="5" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
@@ -2434,7 +2436,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="n">
+      <c r="A62" s="5" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -2442,7 +2444,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="n">
+      <c r="A63" s="5" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
@@ -2450,7 +2452,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="n">
+      <c r="A64" s="5" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">
@@ -2458,7 +2460,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="n">
+      <c r="A65" s="5" t="n">
         <v>46113</v>
       </c>
       <c r="B65" t="n">
@@ -2466,7 +2468,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="n">
+      <c r="A66" s="5" t="n">
         <v>46143</v>
       </c>
       <c r="B66" t="n">
@@ -2474,7 +2476,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="n">
+      <c r="A67" s="5" t="n">
         <v>46174</v>
       </c>
       <c r="B67" t="n">
@@ -2482,7 +2484,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="n">
+      <c r="A68" s="5" t="n">
         <v>46204</v>
       </c>
       <c r="B68" t="n">
@@ -2490,7 +2492,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="3" t="n">
+      <c r="A69" s="5" t="n">
         <v>46235</v>
       </c>
       <c r="B69" t="n">
@@ -2548,7 +2550,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>44286</v>
       </c>
       <c r="B2" t="n">
@@ -2568,7 +2570,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>44377</v>
       </c>
       <c r="B3" t="n">
@@ -2588,7 +2590,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>44469</v>
       </c>
       <c r="B4" t="n">
@@ -2608,7 +2610,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>44561</v>
       </c>
       <c r="B5" t="n">
@@ -2628,7 +2630,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="5" t="n">
         <v>44651</v>
       </c>
       <c r="B6" t="n">
@@ -2648,7 +2650,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="5" t="n">
         <v>44742</v>
       </c>
       <c r="B7" t="n">
@@ -2668,7 +2670,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="5" t="n">
         <v>44834</v>
       </c>
       <c r="B8" t="n">
@@ -2688,7 +2690,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="5" t="n">
         <v>44926</v>
       </c>
       <c r="B9" t="n">
@@ -2708,7 +2710,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="5" t="n">
         <v>45016</v>
       </c>
       <c r="B10" t="n">
@@ -2728,7 +2730,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="5" t="n">
         <v>45107</v>
       </c>
       <c r="B11" t="n">
@@ -2748,7 +2750,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="5" t="n">
         <v>45199</v>
       </c>
       <c r="B12" t="n">
@@ -2768,7 +2770,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="5" t="n">
         <v>45291</v>
       </c>
       <c r="B13" t="n">
@@ -2788,7 +2790,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="5" t="n">
         <v>45382</v>
       </c>
       <c r="B14" t="n">
@@ -2808,7 +2810,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="5" t="n">
         <v>45473</v>
       </c>
       <c r="B15" t="n">
@@ -2828,7 +2830,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="5" t="n">
         <v>45565</v>
       </c>
       <c r="B16" t="n">
@@ -2848,7 +2850,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="5" t="n">
         <v>45657</v>
       </c>
       <c r="B17" t="n">
@@ -2868,7 +2870,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="5" t="n">
         <v>45747</v>
       </c>
       <c r="B18" t="n">
@@ -2888,7 +2890,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="5" t="n">
         <v>45838</v>
       </c>
       <c r="B19" t="n">
@@ -2908,7 +2910,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="5" t="n">
         <v>45930</v>
       </c>
       <c r="B20" t="n">
@@ -2928,7 +2930,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="5" t="n">
         <v>46022</v>
       </c>
       <c r="B21" t="n">
@@ -2948,7 +2950,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="5" t="n">
         <v>46112</v>
       </c>
       <c r="B22" t="n">
@@ -2968,7 +2970,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="5" t="n">
         <v>46203</v>
       </c>
       <c r="B23" t="n">
